--- a/registro_respuestas.xlsx
+++ b/registro_respuestas.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="506" uniqueCount="104">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="949" uniqueCount="173">
   <si>
     <t>fecha_hora</t>
   </si>
@@ -265,12 +265,216 @@
     <t>2026-05-07 18:25:03</t>
   </si>
   <si>
+    <t>2026-05-08 08:45:37</t>
+  </si>
+  <si>
+    <t>2026-05-08 08:49:44</t>
+  </si>
+  <si>
+    <t>2026-05-08 08:50:02</t>
+  </si>
+  <si>
+    <t>2026-05-08 08:50:12</t>
+  </si>
+  <si>
+    <t>2026-05-08 08:50:19</t>
+  </si>
+  <si>
+    <t>2026-05-08 08:50:33</t>
+  </si>
+  <si>
+    <t>2026-05-08 08:50:50</t>
+  </si>
+  <si>
+    <t>2026-05-08 08:51:05</t>
+  </si>
+  <si>
+    <t>2026-05-08 08:51:16</t>
+  </si>
+  <si>
+    <t>2026-05-08 08:51:30</t>
+  </si>
+  <si>
+    <t>2026-05-08 08:51:46</t>
+  </si>
+  <si>
+    <t>2026-05-08 08:51:53</t>
+  </si>
+  <si>
+    <t>2026-05-08 08:52:03</t>
+  </si>
+  <si>
+    <t>2026-05-08 08:52:13</t>
+  </si>
+  <si>
+    <t>2026-05-08 08:52:14</t>
+  </si>
+  <si>
+    <t>2026-05-08 08:52:25</t>
+  </si>
+  <si>
+    <t>2026-05-08 08:52:33</t>
+  </si>
+  <si>
+    <t>2026-05-08 08:52:40</t>
+  </si>
+  <si>
+    <t>2026-05-08 08:52:55</t>
+  </si>
+  <si>
+    <t>2026-05-08 08:53:05</t>
+  </si>
+  <si>
+    <t>2026-05-08 08:53:19</t>
+  </si>
+  <si>
+    <t>2026-05-08 08:53:25</t>
+  </si>
+  <si>
+    <t>2026-05-08 08:53:34</t>
+  </si>
+  <si>
+    <t>2026-05-08 08:53:37</t>
+  </si>
+  <si>
+    <t>2026-05-08 08:53:40</t>
+  </si>
+  <si>
+    <t>2026-05-08 08:53:42</t>
+  </si>
+  <si>
+    <t>2026-05-08 08:54:07</t>
+  </si>
+  <si>
+    <t>2026-05-08 09:20:25</t>
+  </si>
+  <si>
+    <t>2026-05-08 09:20:40</t>
+  </si>
+  <si>
+    <t>2026-05-08 09:20:47</t>
+  </si>
+  <si>
+    <t>2026-05-08 09:20:56</t>
+  </si>
+  <si>
+    <t>2026-05-08 09:21:07</t>
+  </si>
+  <si>
+    <t>2026-05-08 09:21:14</t>
+  </si>
+  <si>
+    <t>2026-05-08 09:21:25</t>
+  </si>
+  <si>
+    <t>2026-05-08 09:21:32</t>
+  </si>
+  <si>
+    <t>2026-05-08 09:21:45</t>
+  </si>
+  <si>
+    <t>2026-05-08 09:22:13</t>
+  </si>
+  <si>
+    <t>2026-05-08 09:28:04</t>
+  </si>
+  <si>
+    <t>2026-05-08 09:28:25</t>
+  </si>
+  <si>
+    <t>2026-05-08 09:28:36</t>
+  </si>
+  <si>
+    <t>2026-05-08 09:28:42</t>
+  </si>
+  <si>
+    <t>2026-05-08 09:28:48</t>
+  </si>
+  <si>
+    <t>2026-05-08 09:28:50</t>
+  </si>
+  <si>
+    <t>2026-05-08 09:29:03</t>
+  </si>
+  <si>
+    <t>2026-05-08 09:29:15</t>
+  </si>
+  <si>
+    <t>2026-05-08 09:29:30</t>
+  </si>
+  <si>
+    <t>2026-05-08 09:29:31</t>
+  </si>
+  <si>
+    <t>2026-05-08 09:29:43</t>
+  </si>
+  <si>
+    <t>2026-05-08 09:29:50</t>
+  </si>
+  <si>
+    <t>2026-05-08 09:29:58</t>
+  </si>
+  <si>
+    <t>2026-05-08 09:30:09</t>
+  </si>
+  <si>
+    <t>2026-05-08 09:30:15</t>
+  </si>
+  <si>
+    <t>2026-05-08 09:30:26</t>
+  </si>
+  <si>
+    <t>2026-05-08 09:30:36</t>
+  </si>
+  <si>
+    <t>2026-05-08 09:30:46</t>
+  </si>
+  <si>
+    <t>2026-05-08 09:30:57</t>
+  </si>
+  <si>
+    <t>2026-05-08 09:31:09</t>
+  </si>
+  <si>
+    <t>2026-05-08 09:31:14</t>
+  </si>
+  <si>
+    <t>2026-05-08 09:31:23</t>
+  </si>
+  <si>
+    <t>2026-05-08 09:31:36</t>
+  </si>
+  <si>
+    <t>2026-05-08 09:31:43</t>
+  </si>
+  <si>
+    <t>2026-05-08 09:31:51</t>
+  </si>
+  <si>
+    <t>2026-05-08 09:32:02</t>
+  </si>
+  <si>
+    <t>2026-05-08 09:32:10</t>
+  </si>
+  <si>
+    <t>2026-05-08 09:32:15</t>
+  </si>
+  <si>
+    <t>2026-05-08 09:32:20</t>
+  </si>
+  <si>
+    <t>2026-05-08 09:32:31</t>
+  </si>
+  <si>
     <t>Carlos</t>
   </si>
   <si>
     <t>Pablo</t>
   </si>
   <si>
+    <t>alejandra</t>
+  </si>
+  <si>
     <t>4° básico</t>
   </si>
   <si>
@@ -326,6 +530,9 @@
   </si>
   <si>
     <t>A</t>
+  </si>
+  <si>
+    <t>None</t>
   </si>
 </sst>
 </file>
@@ -683,7 +890,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L72"/>
+  <dimension ref="A1:L139"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:12">
@@ -729,7 +936,7 @@
         <v>12</v>
       </c>
       <c r="B2" t="s">
-        <v>83</v>
+        <v>150</v>
       </c>
       <c r="C2">
         <v>13</v>
@@ -738,19 +945,19 @@
         <v>14</v>
       </c>
       <c r="F2" t="s">
-        <v>85</v>
+        <v>153</v>
       </c>
       <c r="G2" t="s">
-        <v>88</v>
+        <v>156</v>
       </c>
       <c r="H2" t="s">
-        <v>92</v>
+        <v>160</v>
       </c>
       <c r="I2" t="s">
-        <v>100</v>
+        <v>168</v>
       </c>
       <c r="J2" t="s">
-        <v>100</v>
+        <v>168</v>
       </c>
       <c r="K2" t="b">
         <v>1</v>
@@ -764,7 +971,7 @@
         <v>13</v>
       </c>
       <c r="B3" t="s">
-        <v>83</v>
+        <v>150</v>
       </c>
       <c r="C3">
         <v>13</v>
@@ -773,19 +980,19 @@
         <v>14</v>
       </c>
       <c r="F3" t="s">
-        <v>85</v>
+        <v>153</v>
       </c>
       <c r="G3" t="s">
-        <v>88</v>
+        <v>156</v>
       </c>
       <c r="H3" t="s">
-        <v>92</v>
+        <v>160</v>
       </c>
       <c r="I3" t="s">
-        <v>100</v>
+        <v>168</v>
       </c>
       <c r="J3" t="s">
-        <v>100</v>
+        <v>168</v>
       </c>
       <c r="K3" t="b">
         <v>1</v>
@@ -799,7 +1006,7 @@
         <v>14</v>
       </c>
       <c r="B4" t="s">
-        <v>83</v>
+        <v>150</v>
       </c>
       <c r="C4">
         <v>3</v>
@@ -808,19 +1015,19 @@
         <v>3</v>
       </c>
       <c r="F4" t="s">
-        <v>86</v>
+        <v>154</v>
       </c>
       <c r="G4" t="s">
-        <v>88</v>
+        <v>156</v>
       </c>
       <c r="H4" t="s">
-        <v>93</v>
+        <v>161</v>
       </c>
       <c r="I4" t="s">
-        <v>101</v>
+        <v>169</v>
       </c>
       <c r="J4" t="s">
-        <v>101</v>
+        <v>169</v>
       </c>
       <c r="K4" t="b">
         <v>1</v>
@@ -834,7 +1041,7 @@
         <v>15</v>
       </c>
       <c r="B5" t="s">
-        <v>83</v>
+        <v>150</v>
       </c>
       <c r="C5">
         <v>3</v>
@@ -843,19 +1050,19 @@
         <v>3</v>
       </c>
       <c r="F5" t="s">
-        <v>86</v>
+        <v>154</v>
       </c>
       <c r="G5" t="s">
-        <v>88</v>
+        <v>156</v>
       </c>
       <c r="H5" t="s">
-        <v>93</v>
+        <v>161</v>
       </c>
       <c r="I5" t="s">
-        <v>101</v>
+        <v>169</v>
       </c>
       <c r="J5" t="s">
-        <v>101</v>
+        <v>169</v>
       </c>
       <c r="K5" t="b">
         <v>1</v>
@@ -869,7 +1076,7 @@
         <v>16</v>
       </c>
       <c r="B6" t="s">
-        <v>83</v>
+        <v>150</v>
       </c>
       <c r="C6">
         <v>12</v>
@@ -878,19 +1085,19 @@
         <v>13</v>
       </c>
       <c r="F6" t="s">
-        <v>87</v>
+        <v>155</v>
       </c>
       <c r="G6" t="s">
-        <v>89</v>
+        <v>157</v>
       </c>
       <c r="H6" t="s">
-        <v>94</v>
+        <v>162</v>
       </c>
       <c r="I6" t="s">
-        <v>102</v>
+        <v>170</v>
       </c>
       <c r="J6" t="s">
-        <v>102</v>
+        <v>170</v>
       </c>
       <c r="K6" t="b">
         <v>1</v>
@@ -904,7 +1111,7 @@
         <v>17</v>
       </c>
       <c r="B7" t="s">
-        <v>83</v>
+        <v>150</v>
       </c>
       <c r="C7">
         <v>11</v>
@@ -913,19 +1120,19 @@
         <v>12</v>
       </c>
       <c r="F7" t="s">
-        <v>87</v>
+        <v>155</v>
       </c>
       <c r="G7" t="s">
-        <v>90</v>
+        <v>158</v>
       </c>
       <c r="H7" t="s">
-        <v>95</v>
+        <v>163</v>
       </c>
       <c r="I7" t="s">
-        <v>103</v>
+        <v>171</v>
       </c>
       <c r="J7" t="s">
-        <v>103</v>
+        <v>171</v>
       </c>
       <c r="K7" t="b">
         <v>1</v>
@@ -939,7 +1146,7 @@
         <v>18</v>
       </c>
       <c r="B8" t="s">
-        <v>83</v>
+        <v>150</v>
       </c>
       <c r="C8">
         <v>5</v>
@@ -948,16 +1155,16 @@
         <v>6</v>
       </c>
       <c r="F8" t="s">
-        <v>86</v>
+        <v>154</v>
       </c>
       <c r="G8" t="s">
-        <v>88</v>
+        <v>156</v>
       </c>
       <c r="H8" t="s">
-        <v>93</v>
+        <v>161</v>
       </c>
       <c r="J8" t="s">
-        <v>100</v>
+        <v>168</v>
       </c>
       <c r="K8" t="b">
         <v>0</v>
@@ -971,7 +1178,7 @@
         <v>19</v>
       </c>
       <c r="B9" t="s">
-        <v>83</v>
+        <v>150</v>
       </c>
       <c r="C9">
         <v>4</v>
@@ -980,19 +1187,19 @@
         <v>5</v>
       </c>
       <c r="F9" t="s">
-        <v>86</v>
+        <v>154</v>
       </c>
       <c r="G9" t="s">
-        <v>88</v>
+        <v>156</v>
       </c>
       <c r="H9" t="s">
-        <v>93</v>
+        <v>161</v>
       </c>
       <c r="I9" t="s">
-        <v>101</v>
+        <v>169</v>
       </c>
       <c r="J9" t="s">
-        <v>101</v>
+        <v>169</v>
       </c>
       <c r="K9" t="b">
         <v>1</v>
@@ -1006,7 +1213,7 @@
         <v>20</v>
       </c>
       <c r="B10" t="s">
-        <v>83</v>
+        <v>150</v>
       </c>
       <c r="C10">
         <v>10</v>
@@ -1015,19 +1222,19 @@
         <v>11</v>
       </c>
       <c r="F10" t="s">
-        <v>87</v>
+        <v>155</v>
       </c>
       <c r="G10" t="s">
-        <v>90</v>
+        <v>158</v>
       </c>
       <c r="H10" t="s">
-        <v>95</v>
+        <v>163</v>
       </c>
       <c r="I10" t="s">
-        <v>101</v>
+        <v>169</v>
       </c>
       <c r="J10" t="s">
-        <v>100</v>
+        <v>168</v>
       </c>
       <c r="K10" t="b">
         <v>0</v>
@@ -1041,7 +1248,7 @@
         <v>21</v>
       </c>
       <c r="B11" t="s">
-        <v>83</v>
+        <v>150</v>
       </c>
       <c r="C11">
         <v>8</v>
@@ -1050,19 +1257,19 @@
         <v>9</v>
       </c>
       <c r="F11" t="s">
-        <v>87</v>
+        <v>155</v>
       </c>
       <c r="G11" t="s">
-        <v>91</v>
+        <v>159</v>
       </c>
       <c r="H11" t="s">
-        <v>96</v>
+        <v>164</v>
       </c>
       <c r="I11" t="s">
-        <v>100</v>
+        <v>168</v>
       </c>
       <c r="J11" t="s">
-        <v>100</v>
+        <v>168</v>
       </c>
       <c r="K11" t="b">
         <v>1</v>
@@ -1076,7 +1283,7 @@
         <v>22</v>
       </c>
       <c r="B12" t="s">
-        <v>83</v>
+        <v>150</v>
       </c>
       <c r="C12">
         <v>1</v>
@@ -1085,19 +1292,19 @@
         <v>1</v>
       </c>
       <c r="F12" t="s">
-        <v>87</v>
+        <v>155</v>
       </c>
       <c r="G12" t="s">
-        <v>90</v>
+        <v>158</v>
       </c>
       <c r="H12" t="s">
-        <v>95</v>
+        <v>163</v>
       </c>
       <c r="I12" t="s">
-        <v>101</v>
+        <v>169</v>
       </c>
       <c r="J12" t="s">
-        <v>101</v>
+        <v>169</v>
       </c>
       <c r="K12" t="b">
         <v>1</v>
@@ -1111,7 +1318,7 @@
         <v>23</v>
       </c>
       <c r="B13" t="s">
-        <v>83</v>
+        <v>150</v>
       </c>
       <c r="C13">
         <v>1</v>
@@ -1120,19 +1327,19 @@
         <v>1</v>
       </c>
       <c r="F13" t="s">
-        <v>87</v>
+        <v>155</v>
       </c>
       <c r="G13" t="s">
-        <v>90</v>
+        <v>158</v>
       </c>
       <c r="H13" t="s">
-        <v>95</v>
+        <v>163</v>
       </c>
       <c r="I13" t="s">
-        <v>101</v>
+        <v>169</v>
       </c>
       <c r="J13" t="s">
-        <v>101</v>
+        <v>169</v>
       </c>
       <c r="K13" t="b">
         <v>1</v>
@@ -1146,7 +1353,7 @@
         <v>24</v>
       </c>
       <c r="B14" t="s">
-        <v>83</v>
+        <v>150</v>
       </c>
       <c r="C14">
         <v>3</v>
@@ -1155,19 +1362,19 @@
         <v>4</v>
       </c>
       <c r="F14" t="s">
-        <v>86</v>
+        <v>154</v>
       </c>
       <c r="G14" t="s">
-        <v>88</v>
+        <v>156</v>
       </c>
       <c r="H14" t="s">
-        <v>93</v>
+        <v>161</v>
       </c>
       <c r="I14" t="s">
-        <v>103</v>
+        <v>171</v>
       </c>
       <c r="J14" t="s">
-        <v>103</v>
+        <v>171</v>
       </c>
       <c r="K14" t="b">
         <v>1</v>
@@ -1181,7 +1388,7 @@
         <v>25</v>
       </c>
       <c r="B15" t="s">
-        <v>83</v>
+        <v>150</v>
       </c>
       <c r="C15">
         <v>5</v>
@@ -1190,19 +1397,19 @@
         <v>6</v>
       </c>
       <c r="F15" t="s">
-        <v>86</v>
+        <v>154</v>
       </c>
       <c r="G15" t="s">
-        <v>88</v>
+        <v>156</v>
       </c>
       <c r="H15" t="s">
-        <v>93</v>
+        <v>161</v>
       </c>
       <c r="I15" t="s">
-        <v>100</v>
+        <v>168</v>
       </c>
       <c r="J15" t="s">
-        <v>100</v>
+        <v>168</v>
       </c>
       <c r="K15" t="b">
         <v>1</v>
@@ -1216,7 +1423,7 @@
         <v>26</v>
       </c>
       <c r="B16" t="s">
-        <v>83</v>
+        <v>150</v>
       </c>
       <c r="C16">
         <v>7</v>
@@ -1225,19 +1432,19 @@
         <v>8</v>
       </c>
       <c r="F16" t="s">
-        <v>86</v>
+        <v>154</v>
       </c>
       <c r="G16" t="s">
-        <v>88</v>
+        <v>156</v>
       </c>
       <c r="H16" t="s">
-        <v>93</v>
+        <v>161</v>
       </c>
       <c r="I16" t="s">
-        <v>100</v>
+        <v>168</v>
       </c>
       <c r="J16" t="s">
-        <v>100</v>
+        <v>168</v>
       </c>
       <c r="K16" t="b">
         <v>1</v>
@@ -1251,7 +1458,7 @@
         <v>27</v>
       </c>
       <c r="B17" t="s">
-        <v>83</v>
+        <v>150</v>
       </c>
       <c r="C17">
         <v>6</v>
@@ -1260,19 +1467,19 @@
         <v>7</v>
       </c>
       <c r="F17" t="s">
-        <v>86</v>
+        <v>154</v>
       </c>
       <c r="G17" t="s">
-        <v>88</v>
+        <v>156</v>
       </c>
       <c r="H17" t="s">
-        <v>93</v>
+        <v>161</v>
       </c>
       <c r="I17" t="s">
-        <v>101</v>
+        <v>169</v>
       </c>
       <c r="J17" t="s">
-        <v>101</v>
+        <v>169</v>
       </c>
       <c r="K17" t="b">
         <v>1</v>
@@ -1286,7 +1493,7 @@
         <v>28</v>
       </c>
       <c r="B18" t="s">
-        <v>83</v>
+        <v>150</v>
       </c>
       <c r="C18">
         <v>6</v>
@@ -1295,19 +1502,19 @@
         <v>7</v>
       </c>
       <c r="F18" t="s">
-        <v>86</v>
+        <v>154</v>
       </c>
       <c r="G18" t="s">
-        <v>88</v>
+        <v>156</v>
       </c>
       <c r="H18" t="s">
-        <v>93</v>
+        <v>161</v>
       </c>
       <c r="I18" t="s">
-        <v>101</v>
+        <v>169</v>
       </c>
       <c r="J18" t="s">
-        <v>101</v>
+        <v>169</v>
       </c>
       <c r="K18" t="b">
         <v>1</v>
@@ -1321,7 +1528,7 @@
         <v>29</v>
       </c>
       <c r="B19" t="s">
-        <v>83</v>
+        <v>150</v>
       </c>
       <c r="C19">
         <v>10</v>
@@ -1330,19 +1537,19 @@
         <v>11</v>
       </c>
       <c r="F19" t="s">
-        <v>87</v>
+        <v>155</v>
       </c>
       <c r="G19" t="s">
-        <v>90</v>
+        <v>158</v>
       </c>
       <c r="H19" t="s">
-        <v>95</v>
+        <v>163</v>
       </c>
       <c r="I19" t="s">
-        <v>100</v>
+        <v>168</v>
       </c>
       <c r="J19" t="s">
-        <v>100</v>
+        <v>168</v>
       </c>
       <c r="K19" t="b">
         <v>1</v>
@@ -1356,7 +1563,7 @@
         <v>30</v>
       </c>
       <c r="B20" t="s">
-        <v>83</v>
+        <v>150</v>
       </c>
       <c r="C20">
         <v>8</v>
@@ -1365,19 +1572,19 @@
         <v>9</v>
       </c>
       <c r="F20" t="s">
-        <v>87</v>
+        <v>155</v>
       </c>
       <c r="G20" t="s">
-        <v>91</v>
+        <v>159</v>
       </c>
       <c r="H20" t="s">
-        <v>96</v>
+        <v>164</v>
       </c>
       <c r="I20" t="s">
-        <v>100</v>
+        <v>168</v>
       </c>
       <c r="J20" t="s">
-        <v>100</v>
+        <v>168</v>
       </c>
       <c r="K20" t="b">
         <v>1</v>
@@ -1391,7 +1598,7 @@
         <v>31</v>
       </c>
       <c r="B21" t="s">
-        <v>83</v>
+        <v>150</v>
       </c>
       <c r="C21">
         <v>6</v>
@@ -1400,19 +1607,19 @@
         <v>7</v>
       </c>
       <c r="F21" t="s">
-        <v>86</v>
+        <v>154</v>
       </c>
       <c r="G21" t="s">
-        <v>88</v>
+        <v>156</v>
       </c>
       <c r="H21" t="s">
-        <v>93</v>
+        <v>161</v>
       </c>
       <c r="I21" t="s">
-        <v>101</v>
+        <v>169</v>
       </c>
       <c r="J21" t="s">
-        <v>101</v>
+        <v>169</v>
       </c>
       <c r="K21" t="b">
         <v>1</v>
@@ -1426,7 +1633,7 @@
         <v>32</v>
       </c>
       <c r="B22" t="s">
-        <v>83</v>
+        <v>150</v>
       </c>
       <c r="C22">
         <v>3</v>
@@ -1435,16 +1642,16 @@
         <v>3</v>
       </c>
       <c r="G22" t="s">
-        <v>88</v>
+        <v>156</v>
       </c>
       <c r="H22" t="s">
-        <v>93</v>
+        <v>161</v>
       </c>
       <c r="I22" t="s">
-        <v>101</v>
+        <v>169</v>
       </c>
       <c r="J22" t="s">
-        <v>101</v>
+        <v>169</v>
       </c>
       <c r="K22" t="b">
         <v>1</v>
@@ -1458,7 +1665,7 @@
         <v>33</v>
       </c>
       <c r="B23" t="s">
-        <v>83</v>
+        <v>150</v>
       </c>
       <c r="C23">
         <v>3</v>
@@ -1467,19 +1674,19 @@
         <v>4</v>
       </c>
       <c r="F23" t="s">
-        <v>86</v>
+        <v>154</v>
       </c>
       <c r="G23" t="s">
-        <v>88</v>
+        <v>156</v>
       </c>
       <c r="H23" t="s">
-        <v>93</v>
+        <v>161</v>
       </c>
       <c r="I23" t="s">
-        <v>103</v>
+        <v>171</v>
       </c>
       <c r="J23" t="s">
-        <v>103</v>
+        <v>171</v>
       </c>
       <c r="K23" t="b">
         <v>1</v>
@@ -1493,7 +1700,7 @@
         <v>34</v>
       </c>
       <c r="B24" t="s">
-        <v>83</v>
+        <v>150</v>
       </c>
       <c r="C24">
         <v>9</v>
@@ -1502,19 +1709,19 @@
         <v>10</v>
       </c>
       <c r="F24" t="s">
-        <v>87</v>
+        <v>155</v>
       </c>
       <c r="G24" t="s">
-        <v>91</v>
+        <v>159</v>
       </c>
       <c r="H24" t="s">
-        <v>97</v>
+        <v>165</v>
       </c>
       <c r="I24" t="s">
-        <v>103</v>
+        <v>171</v>
       </c>
       <c r="J24" t="s">
-        <v>103</v>
+        <v>171</v>
       </c>
       <c r="K24" t="b">
         <v>1</v>
@@ -1528,7 +1735,7 @@
         <v>35</v>
       </c>
       <c r="B25" t="s">
-        <v>83</v>
+        <v>150</v>
       </c>
       <c r="C25">
         <v>6</v>
@@ -1537,19 +1744,19 @@
         <v>7</v>
       </c>
       <c r="F25" t="s">
-        <v>86</v>
+        <v>154</v>
       </c>
       <c r="G25" t="s">
-        <v>88</v>
+        <v>156</v>
       </c>
       <c r="H25" t="s">
-        <v>93</v>
+        <v>161</v>
       </c>
       <c r="I25" t="s">
-        <v>101</v>
+        <v>169</v>
       </c>
       <c r="J25" t="s">
-        <v>101</v>
+        <v>169</v>
       </c>
       <c r="K25" t="b">
         <v>1</v>
@@ -1563,7 +1770,7 @@
         <v>36</v>
       </c>
       <c r="B26" t="s">
-        <v>83</v>
+        <v>150</v>
       </c>
       <c r="C26">
         <v>7</v>
@@ -1572,19 +1779,19 @@
         <v>8</v>
       </c>
       <c r="F26" t="s">
-        <v>86</v>
+        <v>154</v>
       </c>
       <c r="G26" t="s">
-        <v>88</v>
+        <v>156</v>
       </c>
       <c r="H26" t="s">
-        <v>93</v>
+        <v>161</v>
       </c>
       <c r="I26" t="s">
-        <v>100</v>
+        <v>168</v>
       </c>
       <c r="J26" t="s">
-        <v>100</v>
+        <v>168</v>
       </c>
       <c r="K26" t="b">
         <v>1</v>
@@ -1598,7 +1805,7 @@
         <v>37</v>
       </c>
       <c r="B27" t="s">
-        <v>83</v>
+        <v>150</v>
       </c>
       <c r="C27">
         <v>2</v>
@@ -1607,19 +1814,19 @@
         <v>2</v>
       </c>
       <c r="F27" t="s">
-        <v>87</v>
+        <v>155</v>
       </c>
       <c r="G27" t="s">
-        <v>88</v>
+        <v>156</v>
       </c>
       <c r="H27" t="s">
-        <v>98</v>
+        <v>166</v>
       </c>
       <c r="I27" t="s">
-        <v>100</v>
+        <v>168</v>
       </c>
       <c r="J27" t="s">
-        <v>100</v>
+        <v>168</v>
       </c>
       <c r="K27" t="b">
         <v>1</v>
@@ -1633,7 +1840,7 @@
         <v>38</v>
       </c>
       <c r="B28" t="s">
-        <v>83</v>
+        <v>150</v>
       </c>
       <c r="C28">
         <v>5</v>
@@ -1642,19 +1849,19 @@
         <v>6</v>
       </c>
       <c r="F28" t="s">
-        <v>86</v>
+        <v>154</v>
       </c>
       <c r="G28" t="s">
-        <v>88</v>
+        <v>156</v>
       </c>
       <c r="H28" t="s">
-        <v>93</v>
+        <v>161</v>
       </c>
       <c r="I28" t="s">
-        <v>100</v>
+        <v>168</v>
       </c>
       <c r="J28" t="s">
-        <v>100</v>
+        <v>168</v>
       </c>
       <c r="K28" t="b">
         <v>1</v>
@@ -1668,7 +1875,7 @@
         <v>39</v>
       </c>
       <c r="B29" t="s">
-        <v>83</v>
+        <v>150</v>
       </c>
       <c r="C29">
         <v>8</v>
@@ -1677,19 +1884,19 @@
         <v>9</v>
       </c>
       <c r="F29" t="s">
-        <v>87</v>
+        <v>155</v>
       </c>
       <c r="G29" t="s">
-        <v>91</v>
+        <v>159</v>
       </c>
       <c r="H29" t="s">
-        <v>96</v>
+        <v>164</v>
       </c>
       <c r="I29" t="s">
-        <v>100</v>
+        <v>168</v>
       </c>
       <c r="J29" t="s">
-        <v>100</v>
+        <v>168</v>
       </c>
       <c r="K29" t="b">
         <v>1</v>
@@ -1703,7 +1910,7 @@
         <v>40</v>
       </c>
       <c r="B30" t="s">
-        <v>83</v>
+        <v>150</v>
       </c>
       <c r="C30">
         <v>6</v>
@@ -1712,19 +1919,19 @@
         <v>7</v>
       </c>
       <c r="F30" t="s">
-        <v>86</v>
+        <v>154</v>
       </c>
       <c r="G30" t="s">
-        <v>88</v>
+        <v>156</v>
       </c>
       <c r="H30" t="s">
-        <v>93</v>
+        <v>161</v>
       </c>
       <c r="I30" t="s">
-        <v>101</v>
+        <v>169</v>
       </c>
       <c r="J30" t="s">
-        <v>101</v>
+        <v>169</v>
       </c>
       <c r="K30" t="b">
         <v>1</v>
@@ -1738,7 +1945,7 @@
         <v>41</v>
       </c>
       <c r="B31" t="s">
-        <v>83</v>
+        <v>150</v>
       </c>
       <c r="C31">
         <v>13</v>
@@ -1747,19 +1954,19 @@
         <v>14</v>
       </c>
       <c r="F31" t="s">
-        <v>85</v>
+        <v>153</v>
       </c>
       <c r="G31" t="s">
-        <v>88</v>
+        <v>156</v>
       </c>
       <c r="H31" t="s">
-        <v>92</v>
+        <v>160</v>
       </c>
       <c r="I31" t="s">
-        <v>100</v>
+        <v>168</v>
       </c>
       <c r="J31" t="s">
-        <v>100</v>
+        <v>168</v>
       </c>
       <c r="K31" t="b">
         <v>1</v>
@@ -1773,7 +1980,7 @@
         <v>42</v>
       </c>
       <c r="B32" t="s">
-        <v>83</v>
+        <v>150</v>
       </c>
       <c r="C32">
         <v>12</v>
@@ -1782,19 +1989,19 @@
         <v>13</v>
       </c>
       <c r="F32" t="s">
-        <v>87</v>
+        <v>155</v>
       </c>
       <c r="G32" t="s">
-        <v>89</v>
+        <v>157</v>
       </c>
       <c r="H32" t="s">
-        <v>94</v>
+        <v>162</v>
       </c>
       <c r="I32" t="s">
-        <v>102</v>
+        <v>170</v>
       </c>
       <c r="J32" t="s">
-        <v>102</v>
+        <v>170</v>
       </c>
       <c r="K32" t="b">
         <v>1</v>
@@ -1808,7 +2015,7 @@
         <v>43</v>
       </c>
       <c r="B33" t="s">
-        <v>83</v>
+        <v>150</v>
       </c>
       <c r="C33">
         <v>2</v>
@@ -1817,19 +2024,19 @@
         <v>2</v>
       </c>
       <c r="F33" t="s">
-        <v>87</v>
+        <v>155</v>
       </c>
       <c r="G33" t="s">
-        <v>88</v>
+        <v>156</v>
       </c>
       <c r="H33" t="s">
-        <v>98</v>
+        <v>166</v>
       </c>
       <c r="I33" t="s">
-        <v>100</v>
+        <v>168</v>
       </c>
       <c r="J33" t="s">
-        <v>100</v>
+        <v>168</v>
       </c>
       <c r="K33" t="b">
         <v>1</v>
@@ -1843,7 +2050,7 @@
         <v>44</v>
       </c>
       <c r="B34" t="s">
-        <v>83</v>
+        <v>150</v>
       </c>
       <c r="C34">
         <v>2</v>
@@ -1852,19 +2059,19 @@
         <v>2</v>
       </c>
       <c r="F34" t="s">
-        <v>87</v>
+        <v>155</v>
       </c>
       <c r="G34" t="s">
-        <v>88</v>
+        <v>156</v>
       </c>
       <c r="H34" t="s">
-        <v>98</v>
+        <v>166</v>
       </c>
       <c r="I34" t="s">
-        <v>100</v>
+        <v>168</v>
       </c>
       <c r="J34" t="s">
-        <v>100</v>
+        <v>168</v>
       </c>
       <c r="K34" t="b">
         <v>1</v>
@@ -1878,7 +2085,7 @@
         <v>45</v>
       </c>
       <c r="B35" t="s">
-        <v>83</v>
+        <v>150</v>
       </c>
       <c r="C35">
         <v>9</v>
@@ -1887,19 +2094,19 @@
         <v>10</v>
       </c>
       <c r="F35" t="s">
-        <v>87</v>
+        <v>155</v>
       </c>
       <c r="G35" t="s">
-        <v>91</v>
+        <v>159</v>
       </c>
       <c r="H35" t="s">
-        <v>97</v>
+        <v>165</v>
       </c>
       <c r="I35" t="s">
-        <v>103</v>
+        <v>171</v>
       </c>
       <c r="J35" t="s">
-        <v>103</v>
+        <v>171</v>
       </c>
       <c r="K35" t="b">
         <v>1</v>
@@ -1913,7 +2120,7 @@
         <v>46</v>
       </c>
       <c r="B36" t="s">
-        <v>83</v>
+        <v>150</v>
       </c>
       <c r="C36">
         <v>9</v>
@@ -1922,19 +2129,19 @@
         <v>10</v>
       </c>
       <c r="F36" t="s">
-        <v>87</v>
+        <v>155</v>
       </c>
       <c r="G36" t="s">
-        <v>91</v>
+        <v>159</v>
       </c>
       <c r="H36" t="s">
-        <v>97</v>
+        <v>165</v>
       </c>
       <c r="I36" t="s">
-        <v>103</v>
+        <v>171</v>
       </c>
       <c r="J36" t="s">
-        <v>103</v>
+        <v>171</v>
       </c>
       <c r="K36" t="b">
         <v>1</v>
@@ -1948,7 +2155,7 @@
         <v>47</v>
       </c>
       <c r="B37" t="s">
-        <v>83</v>
+        <v>150</v>
       </c>
       <c r="C37">
         <v>3</v>
@@ -1957,16 +2164,16 @@
         <v>3</v>
       </c>
       <c r="G37" t="s">
-        <v>88</v>
+        <v>156</v>
       </c>
       <c r="H37" t="s">
-        <v>93</v>
+        <v>161</v>
       </c>
       <c r="I37" t="s">
-        <v>101</v>
+        <v>169</v>
       </c>
       <c r="J37" t="s">
-        <v>101</v>
+        <v>169</v>
       </c>
       <c r="K37" t="b">
         <v>1</v>
@@ -1980,7 +2187,7 @@
         <v>48</v>
       </c>
       <c r="B38" t="s">
-        <v>83</v>
+        <v>150</v>
       </c>
       <c r="C38">
         <v>3</v>
@@ -1989,19 +2196,19 @@
         <v>4</v>
       </c>
       <c r="F38" t="s">
-        <v>86</v>
+        <v>154</v>
       </c>
       <c r="G38" t="s">
-        <v>88</v>
+        <v>156</v>
       </c>
       <c r="H38" t="s">
-        <v>93</v>
+        <v>161</v>
       </c>
       <c r="I38" t="s">
-        <v>103</v>
+        <v>171</v>
       </c>
       <c r="J38" t="s">
-        <v>103</v>
+        <v>171</v>
       </c>
       <c r="K38" t="b">
         <v>1</v>
@@ -2015,7 +2222,7 @@
         <v>49</v>
       </c>
       <c r="B39" t="s">
-        <v>83</v>
+        <v>150</v>
       </c>
       <c r="C39">
         <v>1</v>
@@ -2024,19 +2231,19 @@
         <v>1</v>
       </c>
       <c r="F39" t="s">
-        <v>87</v>
+        <v>155</v>
       </c>
       <c r="G39" t="s">
-        <v>90</v>
+        <v>158</v>
       </c>
       <c r="H39" t="s">
-        <v>95</v>
+        <v>163</v>
       </c>
       <c r="I39" t="s">
-        <v>101</v>
+        <v>169</v>
       </c>
       <c r="J39" t="s">
-        <v>101</v>
+        <v>169</v>
       </c>
       <c r="K39" t="b">
         <v>1</v>
@@ -2050,7 +2257,7 @@
         <v>50</v>
       </c>
       <c r="B40" t="s">
-        <v>83</v>
+        <v>150</v>
       </c>
       <c r="C40">
         <v>7</v>
@@ -2059,19 +2266,19 @@
         <v>8</v>
       </c>
       <c r="F40" t="s">
-        <v>86</v>
+        <v>154</v>
       </c>
       <c r="G40" t="s">
-        <v>88</v>
+        <v>156</v>
       </c>
       <c r="H40" t="s">
-        <v>93</v>
+        <v>161</v>
       </c>
       <c r="I40" t="s">
-        <v>100</v>
+        <v>168</v>
       </c>
       <c r="J40" t="s">
-        <v>100</v>
+        <v>168</v>
       </c>
       <c r="K40" t="b">
         <v>1</v>
@@ -2085,7 +2292,7 @@
         <v>51</v>
       </c>
       <c r="B41" t="s">
-        <v>83</v>
+        <v>150</v>
       </c>
       <c r="C41">
         <v>6</v>
@@ -2094,19 +2301,19 @@
         <v>7</v>
       </c>
       <c r="F41" t="s">
-        <v>86</v>
+        <v>154</v>
       </c>
       <c r="G41" t="s">
-        <v>88</v>
+        <v>156</v>
       </c>
       <c r="H41" t="s">
-        <v>93</v>
+        <v>161</v>
       </c>
       <c r="I41" t="s">
-        <v>101</v>
+        <v>169</v>
       </c>
       <c r="J41" t="s">
-        <v>101</v>
+        <v>169</v>
       </c>
       <c r="K41" t="b">
         <v>1</v>
@@ -2120,7 +2327,7 @@
         <v>52</v>
       </c>
       <c r="B42" t="s">
-        <v>84</v>
+        <v>151</v>
       </c>
       <c r="C42">
         <v>10</v>
@@ -2129,19 +2336,19 @@
         <v>16</v>
       </c>
       <c r="F42" t="s">
-        <v>87</v>
+        <v>155</v>
       </c>
       <c r="G42" t="s">
-        <v>90</v>
+        <v>158</v>
       </c>
       <c r="H42" t="s">
-        <v>95</v>
+        <v>163</v>
       </c>
       <c r="I42" t="s">
-        <v>100</v>
+        <v>168</v>
       </c>
       <c r="J42" t="s">
-        <v>100</v>
+        <v>168</v>
       </c>
       <c r="K42" t="b">
         <v>1</v>
@@ -2155,7 +2362,7 @@
         <v>53</v>
       </c>
       <c r="B43" t="s">
-        <v>84</v>
+        <v>151</v>
       </c>
       <c r="C43">
         <v>9</v>
@@ -2164,19 +2371,19 @@
         <v>15</v>
       </c>
       <c r="F43" t="s">
-        <v>87</v>
+        <v>155</v>
       </c>
       <c r="G43" t="s">
-        <v>91</v>
+        <v>159</v>
       </c>
       <c r="H43" t="s">
-        <v>97</v>
+        <v>165</v>
       </c>
       <c r="I43" t="s">
-        <v>103</v>
+        <v>171</v>
       </c>
       <c r="J43" t="s">
-        <v>103</v>
+        <v>171</v>
       </c>
       <c r="K43" t="b">
         <v>1</v>
@@ -2190,7 +2397,7 @@
         <v>54</v>
       </c>
       <c r="B44" t="s">
-        <v>84</v>
+        <v>151</v>
       </c>
       <c r="C44">
         <v>4</v>
@@ -2199,19 +2406,19 @@
         <v>6</v>
       </c>
       <c r="F44" t="s">
-        <v>86</v>
+        <v>154</v>
       </c>
       <c r="G44" t="s">
-        <v>88</v>
+        <v>156</v>
       </c>
       <c r="H44" t="s">
-        <v>93</v>
+        <v>161</v>
       </c>
       <c r="I44" t="s">
-        <v>101</v>
+        <v>169</v>
       </c>
       <c r="J44" t="s">
-        <v>101</v>
+        <v>169</v>
       </c>
       <c r="K44" t="b">
         <v>1</v>
@@ -2225,7 +2432,7 @@
         <v>55</v>
       </c>
       <c r="B45" t="s">
-        <v>84</v>
+        <v>151</v>
       </c>
       <c r="C45">
         <v>4</v>
@@ -2234,19 +2441,19 @@
         <v>7</v>
       </c>
       <c r="F45" t="s">
-        <v>86</v>
+        <v>154</v>
       </c>
       <c r="G45" t="s">
-        <v>88</v>
+        <v>156</v>
       </c>
       <c r="H45" t="s">
-        <v>93</v>
+        <v>161</v>
       </c>
       <c r="I45" t="s">
-        <v>100</v>
+        <v>168</v>
       </c>
       <c r="J45" t="s">
-        <v>100</v>
+        <v>168</v>
       </c>
       <c r="K45" t="b">
         <v>1</v>
@@ -2260,7 +2467,7 @@
         <v>56</v>
       </c>
       <c r="B46" t="s">
-        <v>84</v>
+        <v>151</v>
       </c>
       <c r="C46">
         <v>4</v>
@@ -2269,19 +2476,19 @@
         <v>8</v>
       </c>
       <c r="F46" t="s">
-        <v>86</v>
+        <v>154</v>
       </c>
       <c r="G46" t="s">
-        <v>88</v>
+        <v>156</v>
       </c>
       <c r="H46" t="s">
-        <v>93</v>
+        <v>161</v>
       </c>
       <c r="I46" t="s">
-        <v>100</v>
+        <v>168</v>
       </c>
       <c r="J46" t="s">
-        <v>100</v>
+        <v>168</v>
       </c>
       <c r="K46" t="b">
         <v>1</v>
@@ -2295,7 +2502,7 @@
         <v>57</v>
       </c>
       <c r="B47" t="s">
-        <v>84</v>
+        <v>151</v>
       </c>
       <c r="C47">
         <v>13</v>
@@ -2304,19 +2511,19 @@
         <v>19</v>
       </c>
       <c r="F47" t="s">
-        <v>85</v>
+        <v>153</v>
       </c>
       <c r="G47" t="s">
-        <v>88</v>
+        <v>156</v>
       </c>
       <c r="H47" t="s">
-        <v>92</v>
+        <v>160</v>
       </c>
       <c r="I47" t="s">
-        <v>100</v>
+        <v>168</v>
       </c>
       <c r="J47" t="s">
-        <v>100</v>
+        <v>168</v>
       </c>
       <c r="K47" t="b">
         <v>1</v>
@@ -2330,7 +2537,7 @@
         <v>58</v>
       </c>
       <c r="B48" t="s">
-        <v>84</v>
+        <v>151</v>
       </c>
       <c r="C48">
         <v>7</v>
@@ -2339,19 +2546,19 @@
         <v>13</v>
       </c>
       <c r="F48" t="s">
-        <v>86</v>
+        <v>154</v>
       </c>
       <c r="G48" t="s">
-        <v>88</v>
+        <v>156</v>
       </c>
       <c r="H48" t="s">
-        <v>93</v>
+        <v>161</v>
       </c>
       <c r="I48" t="s">
-        <v>100</v>
+        <v>168</v>
       </c>
       <c r="J48" t="s">
-        <v>100</v>
+        <v>168</v>
       </c>
       <c r="K48" t="b">
         <v>1</v>
@@ -2365,7 +2572,7 @@
         <v>59</v>
       </c>
       <c r="B49" t="s">
-        <v>84</v>
+        <v>151</v>
       </c>
       <c r="C49">
         <v>7</v>
@@ -2374,19 +2581,19 @@
         <v>13</v>
       </c>
       <c r="F49" t="s">
-        <v>86</v>
+        <v>154</v>
       </c>
       <c r="G49" t="s">
-        <v>88</v>
+        <v>156</v>
       </c>
       <c r="H49" t="s">
-        <v>93</v>
+        <v>161</v>
       </c>
       <c r="I49" t="s">
-        <v>100</v>
+        <v>168</v>
       </c>
       <c r="J49" t="s">
-        <v>100</v>
+        <v>168</v>
       </c>
       <c r="K49" t="b">
         <v>1</v>
@@ -2400,7 +2607,7 @@
         <v>60</v>
       </c>
       <c r="B50" t="s">
-        <v>84</v>
+        <v>151</v>
       </c>
       <c r="C50">
         <v>8</v>
@@ -2409,19 +2616,19 @@
         <v>14</v>
       </c>
       <c r="F50" t="s">
-        <v>87</v>
+        <v>155</v>
       </c>
       <c r="G50" t="s">
-        <v>91</v>
+        <v>159</v>
       </c>
       <c r="H50" t="s">
-        <v>96</v>
+        <v>164</v>
       </c>
       <c r="I50" t="s">
-        <v>100</v>
+        <v>168</v>
       </c>
       <c r="J50" t="s">
-        <v>100</v>
+        <v>168</v>
       </c>
       <c r="K50" t="b">
         <v>1</v>
@@ -2435,7 +2642,7 @@
         <v>61</v>
       </c>
       <c r="B51" t="s">
-        <v>84</v>
+        <v>151</v>
       </c>
       <c r="C51">
         <v>12</v>
@@ -2444,19 +2651,19 @@
         <v>18</v>
       </c>
       <c r="F51" t="s">
-        <v>87</v>
+        <v>155</v>
       </c>
       <c r="G51" t="s">
-        <v>89</v>
+        <v>157</v>
       </c>
       <c r="H51" t="s">
-        <v>94</v>
+        <v>162</v>
       </c>
       <c r="I51" t="s">
-        <v>102</v>
+        <v>170</v>
       </c>
       <c r="J51" t="s">
-        <v>102</v>
+        <v>170</v>
       </c>
       <c r="K51" t="b">
         <v>1</v>
@@ -2470,7 +2677,7 @@
         <v>62</v>
       </c>
       <c r="B52" t="s">
-        <v>84</v>
+        <v>151</v>
       </c>
       <c r="C52">
         <v>14</v>
@@ -2479,19 +2686,19 @@
         <v>20</v>
       </c>
       <c r="F52" t="s">
-        <v>86</v>
+        <v>154</v>
       </c>
       <c r="G52" t="s">
-        <v>88</v>
+        <v>156</v>
       </c>
       <c r="H52" t="s">
-        <v>99</v>
+        <v>167</v>
       </c>
       <c r="I52" t="s">
-        <v>100</v>
+        <v>168</v>
       </c>
       <c r="J52" t="s">
-        <v>100</v>
+        <v>168</v>
       </c>
       <c r="K52" t="b">
         <v>1</v>
@@ -2505,7 +2712,7 @@
         <v>63</v>
       </c>
       <c r="B53" t="s">
-        <v>84</v>
+        <v>151</v>
       </c>
       <c r="C53">
         <v>14</v>
@@ -2514,19 +2721,19 @@
         <v>21</v>
       </c>
       <c r="F53" t="s">
-        <v>86</v>
+        <v>154</v>
       </c>
       <c r="G53" t="s">
-        <v>88</v>
+        <v>156</v>
       </c>
       <c r="H53" t="s">
-        <v>99</v>
+        <v>167</v>
       </c>
       <c r="I53" t="s">
-        <v>101</v>
+        <v>169</v>
       </c>
       <c r="J53" t="s">
-        <v>101</v>
+        <v>169</v>
       </c>
       <c r="K53" t="b">
         <v>1</v>
@@ -2540,7 +2747,7 @@
         <v>64</v>
       </c>
       <c r="B54" t="s">
-        <v>84</v>
+        <v>151</v>
       </c>
       <c r="C54">
         <v>11</v>
@@ -2549,19 +2756,19 @@
         <v>17</v>
       </c>
       <c r="F54" t="s">
-        <v>87</v>
+        <v>155</v>
       </c>
       <c r="G54" t="s">
-        <v>90</v>
+        <v>158</v>
       </c>
       <c r="H54" t="s">
-        <v>95</v>
+        <v>163</v>
       </c>
       <c r="I54" t="s">
-        <v>103</v>
+        <v>171</v>
       </c>
       <c r="J54" t="s">
-        <v>103</v>
+        <v>171</v>
       </c>
       <c r="K54" t="b">
         <v>1</v>
@@ -2575,7 +2782,7 @@
         <v>65</v>
       </c>
       <c r="B55" t="s">
-        <v>84</v>
+        <v>151</v>
       </c>
       <c r="C55">
         <v>6</v>
@@ -2584,19 +2791,19 @@
         <v>10</v>
       </c>
       <c r="F55" t="s">
-        <v>86</v>
+        <v>154</v>
       </c>
       <c r="G55" t="s">
-        <v>88</v>
+        <v>156</v>
       </c>
       <c r="H55" t="s">
-        <v>93</v>
+        <v>161</v>
       </c>
       <c r="I55" t="s">
-        <v>101</v>
+        <v>169</v>
       </c>
       <c r="J55" t="s">
-        <v>101</v>
+        <v>169</v>
       </c>
       <c r="K55" t="b">
         <v>1</v>
@@ -2610,7 +2817,7 @@
         <v>66</v>
       </c>
       <c r="B56" t="s">
-        <v>84</v>
+        <v>151</v>
       </c>
       <c r="C56">
         <v>6</v>
@@ -2619,19 +2826,19 @@
         <v>11</v>
       </c>
       <c r="F56" t="s">
-        <v>86</v>
+        <v>154</v>
       </c>
       <c r="G56" t="s">
-        <v>88</v>
+        <v>156</v>
       </c>
       <c r="H56" t="s">
-        <v>93</v>
+        <v>161</v>
       </c>
       <c r="I56" t="s">
-        <v>100</v>
+        <v>168</v>
       </c>
       <c r="J56" t="s">
-        <v>100</v>
+        <v>168</v>
       </c>
       <c r="K56" t="b">
         <v>1</v>
@@ -2645,7 +2852,7 @@
         <v>67</v>
       </c>
       <c r="B57" t="s">
-        <v>84</v>
+        <v>151</v>
       </c>
       <c r="C57">
         <v>6</v>
@@ -2654,19 +2861,19 @@
         <v>12</v>
       </c>
       <c r="F57" t="s">
-        <v>86</v>
+        <v>154</v>
       </c>
       <c r="G57" t="s">
-        <v>88</v>
+        <v>156</v>
       </c>
       <c r="H57" t="s">
-        <v>93</v>
+        <v>161</v>
       </c>
       <c r="I57" t="s">
-        <v>102</v>
+        <v>170</v>
       </c>
       <c r="J57" t="s">
-        <v>102</v>
+        <v>170</v>
       </c>
       <c r="K57" t="b">
         <v>1</v>
@@ -2680,7 +2887,7 @@
         <v>68</v>
       </c>
       <c r="B58" t="s">
-        <v>84</v>
+        <v>151</v>
       </c>
       <c r="C58">
         <v>2</v>
@@ -2689,19 +2896,19 @@
         <v>2</v>
       </c>
       <c r="F58" t="s">
-        <v>87</v>
+        <v>155</v>
       </c>
       <c r="G58" t="s">
-        <v>88</v>
+        <v>156</v>
       </c>
       <c r="H58" t="s">
-        <v>98</v>
+        <v>166</v>
       </c>
       <c r="I58" t="s">
-        <v>100</v>
+        <v>168</v>
       </c>
       <c r="J58" t="s">
-        <v>100</v>
+        <v>168</v>
       </c>
       <c r="K58" t="b">
         <v>1</v>
@@ -2715,7 +2922,7 @@
         <v>69</v>
       </c>
       <c r="B59" t="s">
-        <v>84</v>
+        <v>151</v>
       </c>
       <c r="C59">
         <v>5</v>
@@ -2724,19 +2931,19 @@
         <v>9</v>
       </c>
       <c r="F59" t="s">
-        <v>86</v>
+        <v>154</v>
       </c>
       <c r="G59" t="s">
-        <v>88</v>
+        <v>156</v>
       </c>
       <c r="H59" t="s">
-        <v>93</v>
+        <v>161</v>
       </c>
       <c r="I59" t="s">
-        <v>100</v>
+        <v>168</v>
       </c>
       <c r="J59" t="s">
-        <v>100</v>
+        <v>168</v>
       </c>
       <c r="K59" t="b">
         <v>1</v>
@@ -2750,7 +2957,7 @@
         <v>70</v>
       </c>
       <c r="B60" t="s">
-        <v>84</v>
+        <v>151</v>
       </c>
       <c r="C60">
         <v>3</v>
@@ -2759,19 +2966,19 @@
         <v>3</v>
       </c>
       <c r="F60" t="s">
-        <v>86</v>
+        <v>154</v>
       </c>
       <c r="G60" t="s">
-        <v>88</v>
+        <v>156</v>
       </c>
       <c r="H60" t="s">
-        <v>93</v>
+        <v>161</v>
       </c>
       <c r="I60" t="s">
-        <v>101</v>
+        <v>169</v>
       </c>
       <c r="J60" t="s">
-        <v>101</v>
+        <v>169</v>
       </c>
       <c r="K60" t="b">
         <v>1</v>
@@ -2785,7 +2992,7 @@
         <v>71</v>
       </c>
       <c r="B61" t="s">
-        <v>84</v>
+        <v>151</v>
       </c>
       <c r="C61">
         <v>3</v>
@@ -2794,19 +3001,19 @@
         <v>4</v>
       </c>
       <c r="F61" t="s">
-        <v>86</v>
+        <v>154</v>
       </c>
       <c r="G61" t="s">
-        <v>88</v>
+        <v>156</v>
       </c>
       <c r="H61" t="s">
-        <v>93</v>
+        <v>161</v>
       </c>
       <c r="I61" t="s">
-        <v>102</v>
+        <v>170</v>
       </c>
       <c r="J61" t="s">
-        <v>102</v>
+        <v>170</v>
       </c>
       <c r="K61" t="b">
         <v>1</v>
@@ -2820,7 +3027,7 @@
         <v>72</v>
       </c>
       <c r="B62" t="s">
-        <v>84</v>
+        <v>151</v>
       </c>
       <c r="C62">
         <v>3</v>
@@ -2829,19 +3036,19 @@
         <v>5</v>
       </c>
       <c r="F62" t="s">
-        <v>86</v>
+        <v>154</v>
       </c>
       <c r="G62" t="s">
-        <v>88</v>
+        <v>156</v>
       </c>
       <c r="H62" t="s">
-        <v>93</v>
+        <v>161</v>
       </c>
       <c r="I62" t="s">
-        <v>103</v>
+        <v>171</v>
       </c>
       <c r="J62" t="s">
-        <v>103</v>
+        <v>171</v>
       </c>
       <c r="K62" t="b">
         <v>1</v>
@@ -2855,7 +3062,7 @@
         <v>73</v>
       </c>
       <c r="B63" t="s">
-        <v>84</v>
+        <v>151</v>
       </c>
       <c r="C63">
         <v>3</v>
@@ -2864,19 +3071,19 @@
         <v>5</v>
       </c>
       <c r="F63" t="s">
-        <v>86</v>
+        <v>154</v>
       </c>
       <c r="G63" t="s">
-        <v>88</v>
+        <v>156</v>
       </c>
       <c r="H63" t="s">
-        <v>93</v>
+        <v>161</v>
       </c>
       <c r="I63" t="s">
-        <v>103</v>
+        <v>171</v>
       </c>
       <c r="J63" t="s">
-        <v>103</v>
+        <v>171</v>
       </c>
       <c r="K63" t="b">
         <v>1</v>
@@ -2890,7 +3097,7 @@
         <v>74</v>
       </c>
       <c r="B64" t="s">
-        <v>84</v>
+        <v>151</v>
       </c>
       <c r="C64">
         <v>1</v>
@@ -2899,19 +3106,19 @@
         <v>1</v>
       </c>
       <c r="F64" t="s">
-        <v>87</v>
+        <v>155</v>
       </c>
       <c r="G64" t="s">
-        <v>90</v>
+        <v>158</v>
       </c>
       <c r="H64" t="s">
-        <v>95</v>
+        <v>163</v>
       </c>
       <c r="I64" t="s">
-        <v>101</v>
+        <v>169</v>
       </c>
       <c r="J64" t="s">
-        <v>101</v>
+        <v>169</v>
       </c>
       <c r="K64" t="b">
         <v>1</v>
@@ -2925,7 +3132,7 @@
         <v>75</v>
       </c>
       <c r="B65" t="s">
-        <v>84</v>
+        <v>151</v>
       </c>
       <c r="C65">
         <v>10</v>
@@ -2934,19 +3141,19 @@
         <v>16</v>
       </c>
       <c r="F65" t="s">
-        <v>87</v>
+        <v>155</v>
       </c>
       <c r="G65" t="s">
-        <v>90</v>
+        <v>158</v>
       </c>
       <c r="H65" t="s">
-        <v>95</v>
+        <v>163</v>
       </c>
       <c r="I65" t="s">
-        <v>100</v>
+        <v>168</v>
       </c>
       <c r="J65" t="s">
-        <v>100</v>
+        <v>168</v>
       </c>
       <c r="K65" t="b">
         <v>1</v>
@@ -2960,7 +3167,7 @@
         <v>76</v>
       </c>
       <c r="B66" t="s">
-        <v>84</v>
+        <v>151</v>
       </c>
       <c r="C66">
         <v>12</v>
@@ -2969,19 +3176,19 @@
         <v>18</v>
       </c>
       <c r="F66" t="s">
-        <v>87</v>
+        <v>155</v>
       </c>
       <c r="G66" t="s">
-        <v>89</v>
+        <v>157</v>
       </c>
       <c r="H66" t="s">
-        <v>94</v>
+        <v>162</v>
       </c>
       <c r="I66" t="s">
-        <v>102</v>
+        <v>170</v>
       </c>
       <c r="J66" t="s">
-        <v>102</v>
+        <v>170</v>
       </c>
       <c r="K66" t="b">
         <v>1</v>
@@ -2995,7 +3202,7 @@
         <v>77</v>
       </c>
       <c r="B67" t="s">
-        <v>84</v>
+        <v>151</v>
       </c>
       <c r="C67">
         <v>4</v>
@@ -3004,19 +3211,19 @@
         <v>6</v>
       </c>
       <c r="F67" t="s">
-        <v>86</v>
+        <v>154</v>
       </c>
       <c r="G67" t="s">
-        <v>88</v>
+        <v>156</v>
       </c>
       <c r="H67" t="s">
-        <v>93</v>
+        <v>161</v>
       </c>
       <c r="I67" t="s">
-        <v>102</v>
+        <v>170</v>
       </c>
       <c r="J67" t="s">
-        <v>101</v>
+        <v>169</v>
       </c>
       <c r="K67" t="b">
         <v>0</v>
@@ -3030,7 +3237,7 @@
         <v>78</v>
       </c>
       <c r="B68" t="s">
-        <v>84</v>
+        <v>151</v>
       </c>
       <c r="C68">
         <v>4</v>
@@ -3039,19 +3246,19 @@
         <v>7</v>
       </c>
       <c r="F68" t="s">
-        <v>86</v>
+        <v>154</v>
       </c>
       <c r="G68" t="s">
-        <v>88</v>
+        <v>156</v>
       </c>
       <c r="H68" t="s">
-        <v>93</v>
+        <v>161</v>
       </c>
       <c r="I68" t="s">
-        <v>100</v>
+        <v>168</v>
       </c>
       <c r="J68" t="s">
-        <v>100</v>
+        <v>168</v>
       </c>
       <c r="K68" t="b">
         <v>1</v>
@@ -3065,7 +3272,7 @@
         <v>79</v>
       </c>
       <c r="B69" t="s">
-        <v>84</v>
+        <v>151</v>
       </c>
       <c r="C69">
         <v>4</v>
@@ -3074,19 +3281,19 @@
         <v>7</v>
       </c>
       <c r="F69" t="s">
-        <v>86</v>
+        <v>154</v>
       </c>
       <c r="G69" t="s">
-        <v>88</v>
+        <v>156</v>
       </c>
       <c r="H69" t="s">
-        <v>93</v>
+        <v>161</v>
       </c>
       <c r="I69" t="s">
-        <v>100</v>
+        <v>168</v>
       </c>
       <c r="J69" t="s">
-        <v>100</v>
+        <v>168</v>
       </c>
       <c r="K69" t="b">
         <v>1</v>
@@ -3100,7 +3307,7 @@
         <v>80</v>
       </c>
       <c r="B70" t="s">
-        <v>84</v>
+        <v>151</v>
       </c>
       <c r="C70">
         <v>4</v>
@@ -3109,19 +3316,19 @@
         <v>8</v>
       </c>
       <c r="F70" t="s">
-        <v>86</v>
+        <v>154</v>
       </c>
       <c r="G70" t="s">
-        <v>88</v>
+        <v>156</v>
       </c>
       <c r="H70" t="s">
-        <v>93</v>
+        <v>161</v>
       </c>
       <c r="I70" t="s">
-        <v>100</v>
+        <v>168</v>
       </c>
       <c r="J70" t="s">
-        <v>100</v>
+        <v>168</v>
       </c>
       <c r="K70" t="b">
         <v>1</v>
@@ -3135,7 +3342,7 @@
         <v>81</v>
       </c>
       <c r="B71" t="s">
-        <v>84</v>
+        <v>151</v>
       </c>
       <c r="C71">
         <v>14</v>
@@ -3144,19 +3351,19 @@
         <v>20</v>
       </c>
       <c r="F71" t="s">
-        <v>86</v>
+        <v>154</v>
       </c>
       <c r="G71" t="s">
-        <v>88</v>
+        <v>156</v>
       </c>
       <c r="H71" t="s">
-        <v>99</v>
+        <v>167</v>
       </c>
       <c r="I71" t="s">
-        <v>100</v>
+        <v>168</v>
       </c>
       <c r="J71" t="s">
-        <v>100</v>
+        <v>168</v>
       </c>
       <c r="K71" t="b">
         <v>1</v>
@@ -3170,7 +3377,7 @@
         <v>82</v>
       </c>
       <c r="B72" t="s">
-        <v>84</v>
+        <v>151</v>
       </c>
       <c r="C72">
         <v>14</v>
@@ -3179,25 +3386,2370 @@
         <v>21</v>
       </c>
       <c r="F72" t="s">
-        <v>86</v>
+        <v>154</v>
       </c>
       <c r="G72" t="s">
-        <v>88</v>
+        <v>156</v>
       </c>
       <c r="H72" t="s">
-        <v>99</v>
+        <v>167</v>
       </c>
       <c r="I72" t="s">
-        <v>101</v>
+        <v>169</v>
       </c>
       <c r="J72" t="s">
-        <v>101</v>
+        <v>169</v>
       </c>
       <c r="K72" t="b">
         <v>1</v>
       </c>
       <c r="L72">
         <v>15</v>
+      </c>
+    </row>
+    <row r="73" spans="1:12">
+      <c r="A73" t="s">
+        <v>83</v>
+      </c>
+      <c r="B73" t="s">
+        <v>150</v>
+      </c>
+      <c r="C73">
+        <v>1</v>
+      </c>
+      <c r="D73">
+        <v>1</v>
+      </c>
+      <c r="F73" t="s">
+        <v>155</v>
+      </c>
+      <c r="G73" t="s">
+        <v>158</v>
+      </c>
+      <c r="H73" t="s">
+        <v>163</v>
+      </c>
+      <c r="I73" t="s">
+        <v>169</v>
+      </c>
+      <c r="J73" t="s">
+        <v>169</v>
+      </c>
+      <c r="K73" t="b">
+        <v>1</v>
+      </c>
+      <c r="L73">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="74" spans="1:12">
+      <c r="A74" t="s">
+        <v>84</v>
+      </c>
+      <c r="B74" t="s">
+        <v>150</v>
+      </c>
+      <c r="C74">
+        <v>1</v>
+      </c>
+      <c r="D74">
+        <v>1</v>
+      </c>
+      <c r="F74" t="s">
+        <v>155</v>
+      </c>
+      <c r="G74" t="s">
+        <v>158</v>
+      </c>
+      <c r="H74" t="s">
+        <v>163</v>
+      </c>
+      <c r="I74" t="s">
+        <v>169</v>
+      </c>
+      <c r="J74" t="s">
+        <v>169</v>
+      </c>
+      <c r="K74" t="b">
+        <v>1</v>
+      </c>
+      <c r="L74">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="75" spans="1:12">
+      <c r="A75" t="s">
+        <v>85</v>
+      </c>
+      <c r="B75" t="s">
+        <v>150</v>
+      </c>
+      <c r="C75">
+        <v>3</v>
+      </c>
+      <c r="D75">
+        <v>3</v>
+      </c>
+      <c r="F75" t="s">
+        <v>154</v>
+      </c>
+      <c r="G75" t="s">
+        <v>156</v>
+      </c>
+      <c r="H75" t="s">
+        <v>161</v>
+      </c>
+      <c r="I75" t="s">
+        <v>169</v>
+      </c>
+      <c r="J75" t="s">
+        <v>169</v>
+      </c>
+      <c r="K75" t="b">
+        <v>1</v>
+      </c>
+      <c r="L75">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="76" spans="1:12">
+      <c r="A76" t="s">
+        <v>86</v>
+      </c>
+      <c r="B76" t="s">
+        <v>150</v>
+      </c>
+      <c r="C76">
+        <v>3</v>
+      </c>
+      <c r="D76">
+        <v>4</v>
+      </c>
+      <c r="F76" t="s">
+        <v>154</v>
+      </c>
+      <c r="G76" t="s">
+        <v>156</v>
+      </c>
+      <c r="H76" t="s">
+        <v>161</v>
+      </c>
+      <c r="I76" t="s">
+        <v>170</v>
+      </c>
+      <c r="J76" t="s">
+        <v>170</v>
+      </c>
+      <c r="K76" t="b">
+        <v>1</v>
+      </c>
+      <c r="L76">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="77" spans="1:12">
+      <c r="A77" t="s">
+        <v>87</v>
+      </c>
+      <c r="B77" t="s">
+        <v>150</v>
+      </c>
+      <c r="C77">
+        <v>3</v>
+      </c>
+      <c r="D77">
+        <v>5</v>
+      </c>
+      <c r="F77" t="s">
+        <v>154</v>
+      </c>
+      <c r="G77" t="s">
+        <v>156</v>
+      </c>
+      <c r="H77" t="s">
+        <v>161</v>
+      </c>
+      <c r="I77" t="s">
+        <v>171</v>
+      </c>
+      <c r="J77" t="s">
+        <v>171</v>
+      </c>
+      <c r="K77" t="b">
+        <v>1</v>
+      </c>
+      <c r="L77">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="78" spans="1:12">
+      <c r="A78" t="s">
+        <v>88</v>
+      </c>
+      <c r="B78" t="s">
+        <v>150</v>
+      </c>
+      <c r="C78">
+        <v>2</v>
+      </c>
+      <c r="D78">
+        <v>2</v>
+      </c>
+      <c r="F78" t="s">
+        <v>155</v>
+      </c>
+      <c r="G78" t="s">
+        <v>156</v>
+      </c>
+      <c r="H78" t="s">
+        <v>166</v>
+      </c>
+      <c r="I78" t="s">
+        <v>168</v>
+      </c>
+      <c r="J78" t="s">
+        <v>168</v>
+      </c>
+      <c r="K78" t="b">
+        <v>1</v>
+      </c>
+      <c r="L78">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="79" spans="1:12">
+      <c r="A79" t="s">
+        <v>89</v>
+      </c>
+      <c r="B79" t="s">
+        <v>150</v>
+      </c>
+      <c r="C79">
+        <v>11</v>
+      </c>
+      <c r="D79">
+        <v>17</v>
+      </c>
+      <c r="F79" t="s">
+        <v>155</v>
+      </c>
+      <c r="G79" t="s">
+        <v>158</v>
+      </c>
+      <c r="H79" t="s">
+        <v>163</v>
+      </c>
+      <c r="I79" t="s">
+        <v>171</v>
+      </c>
+      <c r="J79" t="s">
+        <v>171</v>
+      </c>
+      <c r="K79" t="b">
+        <v>1</v>
+      </c>
+      <c r="L79">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="80" spans="1:12">
+      <c r="A80" t="s">
+        <v>90</v>
+      </c>
+      <c r="B80" t="s">
+        <v>150</v>
+      </c>
+      <c r="C80">
+        <v>7</v>
+      </c>
+      <c r="D80">
+        <v>13</v>
+      </c>
+      <c r="F80" t="s">
+        <v>154</v>
+      </c>
+      <c r="G80" t="s">
+        <v>156</v>
+      </c>
+      <c r="H80" t="s">
+        <v>161</v>
+      </c>
+      <c r="I80" t="s">
+        <v>168</v>
+      </c>
+      <c r="J80" t="s">
+        <v>168</v>
+      </c>
+      <c r="K80" t="b">
+        <v>1</v>
+      </c>
+      <c r="L80">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="81" spans="1:12">
+      <c r="A81" t="s">
+        <v>91</v>
+      </c>
+      <c r="B81" t="s">
+        <v>150</v>
+      </c>
+      <c r="C81">
+        <v>8</v>
+      </c>
+      <c r="D81">
+        <v>14</v>
+      </c>
+      <c r="F81" t="s">
+        <v>155</v>
+      </c>
+      <c r="G81" t="s">
+        <v>159</v>
+      </c>
+      <c r="H81" t="s">
+        <v>164</v>
+      </c>
+      <c r="I81" t="s">
+        <v>168</v>
+      </c>
+      <c r="J81" t="s">
+        <v>168</v>
+      </c>
+      <c r="K81" t="b">
+        <v>1</v>
+      </c>
+      <c r="L81">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="82" spans="1:12">
+      <c r="A82" t="s">
+        <v>92</v>
+      </c>
+      <c r="B82" t="s">
+        <v>150</v>
+      </c>
+      <c r="C82">
+        <v>13</v>
+      </c>
+      <c r="D82">
+        <v>19</v>
+      </c>
+      <c r="F82" t="s">
+        <v>153</v>
+      </c>
+      <c r="G82" t="s">
+        <v>156</v>
+      </c>
+      <c r="H82" t="s">
+        <v>160</v>
+      </c>
+      <c r="I82" t="s">
+        <v>168</v>
+      </c>
+      <c r="J82" t="s">
+        <v>168</v>
+      </c>
+      <c r="K82" t="b">
+        <v>1</v>
+      </c>
+      <c r="L82">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="83" spans="1:12">
+      <c r="A83" t="s">
+        <v>93</v>
+      </c>
+      <c r="B83" t="s">
+        <v>150</v>
+      </c>
+      <c r="C83">
+        <v>6</v>
+      </c>
+      <c r="D83">
+        <v>10</v>
+      </c>
+      <c r="F83" t="s">
+        <v>154</v>
+      </c>
+      <c r="G83" t="s">
+        <v>156</v>
+      </c>
+      <c r="H83" t="s">
+        <v>161</v>
+      </c>
+      <c r="I83" t="s">
+        <v>169</v>
+      </c>
+      <c r="J83" t="s">
+        <v>169</v>
+      </c>
+      <c r="K83" t="b">
+        <v>1</v>
+      </c>
+      <c r="L83">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="84" spans="1:12">
+      <c r="A84" t="s">
+        <v>94</v>
+      </c>
+      <c r="B84" t="s">
+        <v>150</v>
+      </c>
+      <c r="C84">
+        <v>6</v>
+      </c>
+      <c r="D84">
+        <v>11</v>
+      </c>
+      <c r="F84" t="s">
+        <v>154</v>
+      </c>
+      <c r="G84" t="s">
+        <v>156</v>
+      </c>
+      <c r="H84" t="s">
+        <v>161</v>
+      </c>
+      <c r="I84" t="s">
+        <v>168</v>
+      </c>
+      <c r="J84" t="s">
+        <v>168</v>
+      </c>
+      <c r="K84" t="b">
+        <v>1</v>
+      </c>
+      <c r="L84">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="85" spans="1:12">
+      <c r="A85" t="s">
+        <v>95</v>
+      </c>
+      <c r="B85" t="s">
+        <v>150</v>
+      </c>
+      <c r="C85">
+        <v>6</v>
+      </c>
+      <c r="D85">
+        <v>12</v>
+      </c>
+      <c r="F85" t="s">
+        <v>154</v>
+      </c>
+      <c r="G85" t="s">
+        <v>156</v>
+      </c>
+      <c r="H85" t="s">
+        <v>161</v>
+      </c>
+      <c r="I85" t="s">
+        <v>170</v>
+      </c>
+      <c r="J85" t="s">
+        <v>170</v>
+      </c>
+      <c r="K85" t="b">
+        <v>1</v>
+      </c>
+      <c r="L85">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="86" spans="1:12">
+      <c r="A86" t="s">
+        <v>96</v>
+      </c>
+      <c r="B86" t="s">
+        <v>150</v>
+      </c>
+      <c r="C86">
+        <v>9</v>
+      </c>
+      <c r="D86">
+        <v>15</v>
+      </c>
+      <c r="F86" t="s">
+        <v>155</v>
+      </c>
+      <c r="G86" t="s">
+        <v>159</v>
+      </c>
+      <c r="H86" t="s">
+        <v>165</v>
+      </c>
+      <c r="I86" t="s">
+        <v>171</v>
+      </c>
+      <c r="J86" t="s">
+        <v>171</v>
+      </c>
+      <c r="K86" t="b">
+        <v>1</v>
+      </c>
+      <c r="L86">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="87" spans="1:12">
+      <c r="A87" t="s">
+        <v>97</v>
+      </c>
+      <c r="B87" t="s">
+        <v>150</v>
+      </c>
+      <c r="C87">
+        <v>9</v>
+      </c>
+      <c r="D87">
+        <v>15</v>
+      </c>
+      <c r="F87" t="s">
+        <v>155</v>
+      </c>
+      <c r="G87" t="s">
+        <v>159</v>
+      </c>
+      <c r="H87" t="s">
+        <v>165</v>
+      </c>
+      <c r="I87" t="s">
+        <v>171</v>
+      </c>
+      <c r="J87" t="s">
+        <v>171</v>
+      </c>
+      <c r="K87" t="b">
+        <v>1</v>
+      </c>
+      <c r="L87">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="88" spans="1:12">
+      <c r="A88" t="s">
+        <v>98</v>
+      </c>
+      <c r="B88" t="s">
+        <v>150</v>
+      </c>
+      <c r="C88">
+        <v>4</v>
+      </c>
+      <c r="D88">
+        <v>6</v>
+      </c>
+      <c r="F88" t="s">
+        <v>154</v>
+      </c>
+      <c r="G88" t="s">
+        <v>156</v>
+      </c>
+      <c r="H88" t="s">
+        <v>161</v>
+      </c>
+      <c r="I88" t="s">
+        <v>169</v>
+      </c>
+      <c r="J88" t="s">
+        <v>169</v>
+      </c>
+      <c r="K88" t="b">
+        <v>1</v>
+      </c>
+      <c r="L88">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="89" spans="1:12">
+      <c r="A89" t="s">
+        <v>99</v>
+      </c>
+      <c r="B89" t="s">
+        <v>150</v>
+      </c>
+      <c r="C89">
+        <v>4</v>
+      </c>
+      <c r="D89">
+        <v>7</v>
+      </c>
+      <c r="F89" t="s">
+        <v>154</v>
+      </c>
+      <c r="G89" t="s">
+        <v>156</v>
+      </c>
+      <c r="H89" t="s">
+        <v>161</v>
+      </c>
+      <c r="I89" t="s">
+        <v>168</v>
+      </c>
+      <c r="J89" t="s">
+        <v>168</v>
+      </c>
+      <c r="K89" t="b">
+        <v>1</v>
+      </c>
+      <c r="L89">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="90" spans="1:12">
+      <c r="A90" t="s">
+        <v>100</v>
+      </c>
+      <c r="B90" t="s">
+        <v>150</v>
+      </c>
+      <c r="C90">
+        <v>4</v>
+      </c>
+      <c r="D90">
+        <v>8</v>
+      </c>
+      <c r="F90" t="s">
+        <v>154</v>
+      </c>
+      <c r="G90" t="s">
+        <v>156</v>
+      </c>
+      <c r="H90" t="s">
+        <v>161</v>
+      </c>
+      <c r="I90" t="s">
+        <v>168</v>
+      </c>
+      <c r="J90" t="s">
+        <v>168</v>
+      </c>
+      <c r="K90" t="b">
+        <v>1</v>
+      </c>
+      <c r="L90">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="91" spans="1:12">
+      <c r="A91" t="s">
+        <v>101</v>
+      </c>
+      <c r="B91" t="s">
+        <v>150</v>
+      </c>
+      <c r="C91">
+        <v>14</v>
+      </c>
+      <c r="D91">
+        <v>20</v>
+      </c>
+      <c r="F91" t="s">
+        <v>154</v>
+      </c>
+      <c r="G91" t="s">
+        <v>156</v>
+      </c>
+      <c r="H91" t="s">
+        <v>167</v>
+      </c>
+      <c r="I91" t="s">
+        <v>169</v>
+      </c>
+      <c r="J91" t="s">
+        <v>168</v>
+      </c>
+      <c r="K91" t="b">
+        <v>0</v>
+      </c>
+      <c r="L91">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="1:12">
+      <c r="A92" t="s">
+        <v>102</v>
+      </c>
+      <c r="B92" t="s">
+        <v>150</v>
+      </c>
+      <c r="C92">
+        <v>14</v>
+      </c>
+      <c r="D92">
+        <v>21</v>
+      </c>
+      <c r="F92" t="s">
+        <v>154</v>
+      </c>
+      <c r="G92" t="s">
+        <v>156</v>
+      </c>
+      <c r="H92" t="s">
+        <v>167</v>
+      </c>
+      <c r="I92" t="s">
+        <v>169</v>
+      </c>
+      <c r="J92" t="s">
+        <v>169</v>
+      </c>
+      <c r="K92" t="b">
+        <v>1</v>
+      </c>
+      <c r="L92">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="93" spans="1:12">
+      <c r="A93" t="s">
+        <v>103</v>
+      </c>
+      <c r="B93" t="s">
+        <v>150</v>
+      </c>
+      <c r="C93">
+        <v>15</v>
+      </c>
+      <c r="D93">
+        <v>22</v>
+      </c>
+      <c r="F93" t="s">
+        <v>154</v>
+      </c>
+      <c r="G93" t="s">
+        <v>156</v>
+      </c>
+      <c r="H93" t="s">
+        <v>161</v>
+      </c>
+      <c r="I93">
+        <v>30</v>
+      </c>
+      <c r="J93">
+        <v>30</v>
+      </c>
+      <c r="K93" t="b">
+        <v>1</v>
+      </c>
+      <c r="L93">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="94" spans="1:12">
+      <c r="A94" t="s">
+        <v>104</v>
+      </c>
+      <c r="B94" t="s">
+        <v>150</v>
+      </c>
+      <c r="C94">
+        <v>15</v>
+      </c>
+      <c r="D94">
+        <v>22</v>
+      </c>
+      <c r="F94" t="s">
+        <v>154</v>
+      </c>
+      <c r="G94" t="s">
+        <v>156</v>
+      </c>
+      <c r="H94" t="s">
+        <v>161</v>
+      </c>
+      <c r="I94">
+        <v>30</v>
+      </c>
+      <c r="J94">
+        <v>30</v>
+      </c>
+      <c r="K94" t="b">
+        <v>1</v>
+      </c>
+      <c r="L94">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="95" spans="1:12">
+      <c r="A95" t="s">
+        <v>105</v>
+      </c>
+      <c r="B95" t="s">
+        <v>150</v>
+      </c>
+      <c r="C95">
+        <v>15</v>
+      </c>
+      <c r="D95">
+        <v>23</v>
+      </c>
+      <c r="F95" t="s">
+        <v>154</v>
+      </c>
+      <c r="G95" t="s">
+        <v>156</v>
+      </c>
+      <c r="H95" t="s">
+        <v>161</v>
+      </c>
+      <c r="I95">
+        <v>24</v>
+      </c>
+      <c r="J95">
+        <v>24</v>
+      </c>
+      <c r="K95" t="b">
+        <v>1</v>
+      </c>
+      <c r="L95">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="96" spans="1:12">
+      <c r="A96" t="s">
+        <v>106</v>
+      </c>
+      <c r="B96" t="s">
+        <v>150</v>
+      </c>
+      <c r="C96">
+        <v>15</v>
+      </c>
+      <c r="D96">
+        <v>23</v>
+      </c>
+      <c r="F96" t="s">
+        <v>154</v>
+      </c>
+      <c r="G96" t="s">
+        <v>156</v>
+      </c>
+      <c r="H96" t="s">
+        <v>161</v>
+      </c>
+      <c r="I96">
+        <v>24</v>
+      </c>
+      <c r="J96">
+        <v>24</v>
+      </c>
+      <c r="K96" t="b">
+        <v>1</v>
+      </c>
+      <c r="L96">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="97" spans="1:12">
+      <c r="A97" t="s">
+        <v>107</v>
+      </c>
+      <c r="B97" t="s">
+        <v>150</v>
+      </c>
+      <c r="C97">
+        <v>15</v>
+      </c>
+      <c r="D97">
+        <v>23</v>
+      </c>
+      <c r="F97" t="s">
+        <v>154</v>
+      </c>
+      <c r="G97" t="s">
+        <v>156</v>
+      </c>
+      <c r="H97" t="s">
+        <v>161</v>
+      </c>
+      <c r="I97">
+        <v>24</v>
+      </c>
+      <c r="J97">
+        <v>24</v>
+      </c>
+      <c r="K97" t="b">
+        <v>1</v>
+      </c>
+      <c r="L97">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="98" spans="1:12">
+      <c r="A98" t="s">
+        <v>108</v>
+      </c>
+      <c r="B98" t="s">
+        <v>150</v>
+      </c>
+      <c r="C98">
+        <v>15</v>
+      </c>
+      <c r="D98">
+        <v>23</v>
+      </c>
+      <c r="F98" t="s">
+        <v>154</v>
+      </c>
+      <c r="G98" t="s">
+        <v>156</v>
+      </c>
+      <c r="H98" t="s">
+        <v>161</v>
+      </c>
+      <c r="I98">
+        <v>24</v>
+      </c>
+      <c r="J98">
+        <v>24</v>
+      </c>
+      <c r="K98" t="b">
+        <v>1</v>
+      </c>
+      <c r="L98">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="99" spans="1:12">
+      <c r="A99" t="s">
+        <v>109</v>
+      </c>
+      <c r="B99" t="s">
+        <v>150</v>
+      </c>
+      <c r="C99">
+        <v>15</v>
+      </c>
+      <c r="D99">
+        <v>24</v>
+      </c>
+      <c r="F99" t="s">
+        <v>154</v>
+      </c>
+      <c r="G99" t="s">
+        <v>156</v>
+      </c>
+      <c r="H99" t="s">
+        <v>161</v>
+      </c>
+      <c r="I99">
+        <v>8</v>
+      </c>
+      <c r="J99">
+        <v>7</v>
+      </c>
+      <c r="K99" t="b">
+        <v>0</v>
+      </c>
+      <c r="L99">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="1:12">
+      <c r="A100" t="s">
+        <v>110</v>
+      </c>
+      <c r="B100" t="s">
+        <v>150</v>
+      </c>
+      <c r="C100">
+        <v>5</v>
+      </c>
+      <c r="D100">
+        <v>9</v>
+      </c>
+      <c r="F100" t="s">
+        <v>154</v>
+      </c>
+      <c r="G100" t="s">
+        <v>156</v>
+      </c>
+      <c r="H100" t="s">
+        <v>161</v>
+      </c>
+      <c r="I100" t="s">
+        <v>170</v>
+      </c>
+      <c r="J100" t="s">
+        <v>168</v>
+      </c>
+      <c r="K100" t="b">
+        <v>0</v>
+      </c>
+      <c r="L100">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101" spans="1:12">
+      <c r="A101" t="s">
+        <v>111</v>
+      </c>
+      <c r="B101" t="s">
+        <v>150</v>
+      </c>
+      <c r="C101">
+        <v>10</v>
+      </c>
+      <c r="D101">
+        <v>16</v>
+      </c>
+      <c r="F101" t="s">
+        <v>155</v>
+      </c>
+      <c r="G101" t="s">
+        <v>158</v>
+      </c>
+      <c r="H101" t="s">
+        <v>163</v>
+      </c>
+      <c r="I101" t="s">
+        <v>168</v>
+      </c>
+      <c r="J101" t="s">
+        <v>168</v>
+      </c>
+      <c r="K101" t="b">
+        <v>1</v>
+      </c>
+      <c r="L101">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="102" spans="1:12">
+      <c r="A102" t="s">
+        <v>112</v>
+      </c>
+      <c r="B102" t="s">
+        <v>150</v>
+      </c>
+      <c r="C102">
+        <v>13</v>
+      </c>
+      <c r="D102">
+        <v>19</v>
+      </c>
+      <c r="F102" t="s">
+        <v>153</v>
+      </c>
+      <c r="G102" t="s">
+        <v>156</v>
+      </c>
+      <c r="H102" t="s">
+        <v>160</v>
+      </c>
+      <c r="I102" t="s">
+        <v>168</v>
+      </c>
+      <c r="J102" t="s">
+        <v>168</v>
+      </c>
+      <c r="K102" t="b">
+        <v>1</v>
+      </c>
+      <c r="L102">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="103" spans="1:12">
+      <c r="A103" t="s">
+        <v>113</v>
+      </c>
+      <c r="B103" t="s">
+        <v>150</v>
+      </c>
+      <c r="C103">
+        <v>8</v>
+      </c>
+      <c r="D103">
+        <v>14</v>
+      </c>
+      <c r="F103" t="s">
+        <v>155</v>
+      </c>
+      <c r="G103" t="s">
+        <v>159</v>
+      </c>
+      <c r="H103" t="s">
+        <v>164</v>
+      </c>
+      <c r="I103" t="s">
+        <v>168</v>
+      </c>
+      <c r="J103" t="s">
+        <v>168</v>
+      </c>
+      <c r="K103" t="b">
+        <v>1</v>
+      </c>
+      <c r="L103">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="104" spans="1:12">
+      <c r="A104" t="s">
+        <v>114</v>
+      </c>
+      <c r="B104" t="s">
+        <v>150</v>
+      </c>
+      <c r="C104">
+        <v>11</v>
+      </c>
+      <c r="D104">
+        <v>17</v>
+      </c>
+      <c r="F104" t="s">
+        <v>155</v>
+      </c>
+      <c r="G104" t="s">
+        <v>158</v>
+      </c>
+      <c r="H104" t="s">
+        <v>163</v>
+      </c>
+      <c r="I104" t="s">
+        <v>171</v>
+      </c>
+      <c r="J104" t="s">
+        <v>171</v>
+      </c>
+      <c r="K104" t="b">
+        <v>1</v>
+      </c>
+      <c r="L104">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="105" spans="1:12">
+      <c r="A105" t="s">
+        <v>115</v>
+      </c>
+      <c r="B105" t="s">
+        <v>150</v>
+      </c>
+      <c r="C105">
+        <v>2</v>
+      </c>
+      <c r="D105">
+        <v>2</v>
+      </c>
+      <c r="F105" t="s">
+        <v>155</v>
+      </c>
+      <c r="G105" t="s">
+        <v>156</v>
+      </c>
+      <c r="H105" t="s">
+        <v>166</v>
+      </c>
+      <c r="I105" t="s">
+        <v>168</v>
+      </c>
+      <c r="J105" t="s">
+        <v>168</v>
+      </c>
+      <c r="K105" t="b">
+        <v>1</v>
+      </c>
+      <c r="L105">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="106" spans="1:12">
+      <c r="A106" t="s">
+        <v>116</v>
+      </c>
+      <c r="B106" t="s">
+        <v>150</v>
+      </c>
+      <c r="C106">
+        <v>15</v>
+      </c>
+      <c r="D106">
+        <v>22</v>
+      </c>
+      <c r="F106" t="s">
+        <v>154</v>
+      </c>
+      <c r="G106" t="s">
+        <v>156</v>
+      </c>
+      <c r="H106" t="s">
+        <v>161</v>
+      </c>
+      <c r="I106">
+        <v>30</v>
+      </c>
+      <c r="J106">
+        <v>30</v>
+      </c>
+      <c r="K106" t="b">
+        <v>1</v>
+      </c>
+      <c r="L106">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="107" spans="1:12">
+      <c r="A107" t="s">
+        <v>117</v>
+      </c>
+      <c r="B107" t="s">
+        <v>150</v>
+      </c>
+      <c r="C107">
+        <v>15</v>
+      </c>
+      <c r="D107">
+        <v>23</v>
+      </c>
+      <c r="F107" t="s">
+        <v>154</v>
+      </c>
+      <c r="G107" t="s">
+        <v>156</v>
+      </c>
+      <c r="H107" t="s">
+        <v>161</v>
+      </c>
+      <c r="I107">
+        <v>24</v>
+      </c>
+      <c r="J107">
+        <v>24</v>
+      </c>
+      <c r="K107" t="b">
+        <v>1</v>
+      </c>
+      <c r="L107">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="108" spans="1:12">
+      <c r="A108" t="s">
+        <v>118</v>
+      </c>
+      <c r="B108" t="s">
+        <v>150</v>
+      </c>
+      <c r="C108">
+        <v>15</v>
+      </c>
+      <c r="D108">
+        <v>24</v>
+      </c>
+      <c r="F108" t="s">
+        <v>154</v>
+      </c>
+      <c r="G108" t="s">
+        <v>156</v>
+      </c>
+      <c r="H108" t="s">
+        <v>161</v>
+      </c>
+      <c r="I108">
+        <v>7</v>
+      </c>
+      <c r="J108">
+        <v>7</v>
+      </c>
+      <c r="K108" t="b">
+        <v>1</v>
+      </c>
+      <c r="L108">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="109" spans="1:12">
+      <c r="A109" t="s">
+        <v>119</v>
+      </c>
+      <c r="B109" t="s">
+        <v>150</v>
+      </c>
+      <c r="C109">
+        <v>1</v>
+      </c>
+      <c r="D109">
+        <v>1</v>
+      </c>
+      <c r="F109" t="s">
+        <v>155</v>
+      </c>
+      <c r="G109" t="s">
+        <v>158</v>
+      </c>
+      <c r="H109" t="s">
+        <v>163</v>
+      </c>
+      <c r="I109" t="s">
+        <v>169</v>
+      </c>
+      <c r="J109" t="s">
+        <v>169</v>
+      </c>
+      <c r="K109" t="b">
+        <v>1</v>
+      </c>
+      <c r="L109">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="110" spans="1:12">
+      <c r="A110" t="s">
+        <v>120</v>
+      </c>
+      <c r="B110" t="s">
+        <v>152</v>
+      </c>
+      <c r="C110">
+        <v>7</v>
+      </c>
+      <c r="D110">
+        <v>13</v>
+      </c>
+      <c r="F110" t="s">
+        <v>154</v>
+      </c>
+      <c r="G110" t="s">
+        <v>156</v>
+      </c>
+      <c r="H110" t="s">
+        <v>161</v>
+      </c>
+      <c r="I110" t="s">
+        <v>171</v>
+      </c>
+      <c r="J110" t="s">
+        <v>168</v>
+      </c>
+      <c r="K110" t="b">
+        <v>0</v>
+      </c>
+      <c r="L110">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="111" spans="1:12">
+      <c r="A111" t="s">
+        <v>121</v>
+      </c>
+      <c r="B111" t="s">
+        <v>152</v>
+      </c>
+      <c r="C111">
+        <v>1</v>
+      </c>
+      <c r="D111">
+        <v>1</v>
+      </c>
+      <c r="F111" t="s">
+        <v>155</v>
+      </c>
+      <c r="G111" t="s">
+        <v>158</v>
+      </c>
+      <c r="H111" t="s">
+        <v>163</v>
+      </c>
+      <c r="I111" t="s">
+        <v>169</v>
+      </c>
+      <c r="J111" t="s">
+        <v>169</v>
+      </c>
+      <c r="K111" t="b">
+        <v>1</v>
+      </c>
+      <c r="L111">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="112" spans="1:12">
+      <c r="A112" t="s">
+        <v>122</v>
+      </c>
+      <c r="B112" t="s">
+        <v>152</v>
+      </c>
+      <c r="C112">
+        <v>3</v>
+      </c>
+      <c r="D112">
+        <v>3</v>
+      </c>
+      <c r="F112" t="s">
+        <v>154</v>
+      </c>
+      <c r="G112" t="s">
+        <v>156</v>
+      </c>
+      <c r="H112" t="s">
+        <v>161</v>
+      </c>
+      <c r="I112" t="s">
+        <v>169</v>
+      </c>
+      <c r="J112" t="s">
+        <v>169</v>
+      </c>
+      <c r="K112" t="b">
+        <v>1</v>
+      </c>
+      <c r="L112">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="113" spans="1:12">
+      <c r="A113" t="s">
+        <v>123</v>
+      </c>
+      <c r="B113" t="s">
+        <v>152</v>
+      </c>
+      <c r="C113">
+        <v>3</v>
+      </c>
+      <c r="D113">
+        <v>4</v>
+      </c>
+      <c r="F113" t="s">
+        <v>154</v>
+      </c>
+      <c r="G113" t="s">
+        <v>156</v>
+      </c>
+      <c r="H113" t="s">
+        <v>161</v>
+      </c>
+      <c r="I113" t="s">
+        <v>170</v>
+      </c>
+      <c r="J113" t="s">
+        <v>170</v>
+      </c>
+      <c r="K113" t="b">
+        <v>1</v>
+      </c>
+      <c r="L113">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="114" spans="1:12">
+      <c r="A114" t="s">
+        <v>124</v>
+      </c>
+      <c r="B114" t="s">
+        <v>152</v>
+      </c>
+      <c r="C114">
+        <v>3</v>
+      </c>
+      <c r="D114">
+        <v>5</v>
+      </c>
+      <c r="F114" t="s">
+        <v>154</v>
+      </c>
+      <c r="G114" t="s">
+        <v>156</v>
+      </c>
+      <c r="H114" t="s">
+        <v>161</v>
+      </c>
+      <c r="I114" t="s">
+        <v>171</v>
+      </c>
+      <c r="J114" t="s">
+        <v>171</v>
+      </c>
+      <c r="K114" t="b">
+        <v>1</v>
+      </c>
+      <c r="L114">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="115" spans="1:12">
+      <c r="A115" t="s">
+        <v>125</v>
+      </c>
+      <c r="B115" t="s">
+        <v>152</v>
+      </c>
+      <c r="C115">
+        <v>3</v>
+      </c>
+      <c r="D115">
+        <v>5</v>
+      </c>
+      <c r="F115" t="s">
+        <v>154</v>
+      </c>
+      <c r="G115" t="s">
+        <v>156</v>
+      </c>
+      <c r="H115" t="s">
+        <v>161</v>
+      </c>
+      <c r="I115" t="s">
+        <v>171</v>
+      </c>
+      <c r="J115" t="s">
+        <v>171</v>
+      </c>
+      <c r="K115" t="b">
+        <v>1</v>
+      </c>
+      <c r="L115">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="116" spans="1:12">
+      <c r="A116" t="s">
+        <v>126</v>
+      </c>
+      <c r="B116" t="s">
+        <v>152</v>
+      </c>
+      <c r="C116">
+        <v>10</v>
+      </c>
+      <c r="D116">
+        <v>16</v>
+      </c>
+      <c r="F116" t="s">
+        <v>155</v>
+      </c>
+      <c r="G116" t="s">
+        <v>158</v>
+      </c>
+      <c r="H116" t="s">
+        <v>163</v>
+      </c>
+      <c r="I116" t="s">
+        <v>168</v>
+      </c>
+      <c r="J116" t="s">
+        <v>168</v>
+      </c>
+      <c r="K116" t="b">
+        <v>1</v>
+      </c>
+      <c r="L116">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="117" spans="1:12">
+      <c r="A117" t="s">
+        <v>127</v>
+      </c>
+      <c r="B117" t="s">
+        <v>152</v>
+      </c>
+      <c r="C117">
+        <v>14</v>
+      </c>
+      <c r="D117">
+        <v>20</v>
+      </c>
+      <c r="F117" t="s">
+        <v>154</v>
+      </c>
+      <c r="G117" t="s">
+        <v>156</v>
+      </c>
+      <c r="H117" t="s">
+        <v>167</v>
+      </c>
+      <c r="I117" t="s">
+        <v>169</v>
+      </c>
+      <c r="J117" t="s">
+        <v>168</v>
+      </c>
+      <c r="K117" t="b">
+        <v>0</v>
+      </c>
+      <c r="L117">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="118" spans="1:12">
+      <c r="A118" t="s">
+        <v>128</v>
+      </c>
+      <c r="B118" t="s">
+        <v>152</v>
+      </c>
+      <c r="C118">
+        <v>14</v>
+      </c>
+      <c r="D118">
+        <v>21</v>
+      </c>
+      <c r="F118" t="s">
+        <v>154</v>
+      </c>
+      <c r="G118" t="s">
+        <v>156</v>
+      </c>
+      <c r="H118" t="s">
+        <v>167</v>
+      </c>
+      <c r="I118" t="s">
+        <v>169</v>
+      </c>
+      <c r="J118" t="s">
+        <v>169</v>
+      </c>
+      <c r="K118" t="b">
+        <v>1</v>
+      </c>
+      <c r="L118">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="119" spans="1:12">
+      <c r="A119" t="s">
+        <v>129</v>
+      </c>
+      <c r="B119" t="s">
+        <v>152</v>
+      </c>
+      <c r="C119">
+        <v>14</v>
+      </c>
+      <c r="D119">
+        <v>21</v>
+      </c>
+      <c r="F119" t="s">
+        <v>154</v>
+      </c>
+      <c r="G119" t="s">
+        <v>156</v>
+      </c>
+      <c r="H119" t="s">
+        <v>167</v>
+      </c>
+      <c r="I119" t="s">
+        <v>169</v>
+      </c>
+      <c r="J119" t="s">
+        <v>169</v>
+      </c>
+      <c r="K119" t="b">
+        <v>1</v>
+      </c>
+      <c r="L119">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="120" spans="1:12">
+      <c r="A120" t="s">
+        <v>130</v>
+      </c>
+      <c r="B120" t="s">
+        <v>152</v>
+      </c>
+      <c r="C120">
+        <v>5</v>
+      </c>
+      <c r="D120">
+        <v>9</v>
+      </c>
+      <c r="F120" t="s">
+        <v>154</v>
+      </c>
+      <c r="G120" t="s">
+        <v>156</v>
+      </c>
+      <c r="H120" t="s">
+        <v>161</v>
+      </c>
+      <c r="I120" t="s">
+        <v>168</v>
+      </c>
+      <c r="J120" t="s">
+        <v>168</v>
+      </c>
+      <c r="K120" t="b">
+        <v>1</v>
+      </c>
+      <c r="L120">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="121" spans="1:12">
+      <c r="A121" t="s">
+        <v>131</v>
+      </c>
+      <c r="B121" t="s">
+        <v>152</v>
+      </c>
+      <c r="C121">
+        <v>2</v>
+      </c>
+      <c r="D121">
+        <v>2</v>
+      </c>
+      <c r="F121" t="s">
+        <v>155</v>
+      </c>
+      <c r="G121" t="s">
+        <v>156</v>
+      </c>
+      <c r="H121" t="s">
+        <v>166</v>
+      </c>
+      <c r="I121" t="s">
+        <v>168</v>
+      </c>
+      <c r="J121" t="s">
+        <v>168</v>
+      </c>
+      <c r="K121" t="b">
+        <v>1</v>
+      </c>
+      <c r="L121">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="122" spans="1:12">
+      <c r="A122" t="s">
+        <v>132</v>
+      </c>
+      <c r="B122" t="s">
+        <v>152</v>
+      </c>
+      <c r="C122">
+        <v>6</v>
+      </c>
+      <c r="D122">
+        <v>10</v>
+      </c>
+      <c r="F122" t="s">
+        <v>154</v>
+      </c>
+      <c r="G122" t="s">
+        <v>156</v>
+      </c>
+      <c r="H122" t="s">
+        <v>161</v>
+      </c>
+      <c r="I122" t="s">
+        <v>169</v>
+      </c>
+      <c r="J122" t="s">
+        <v>169</v>
+      </c>
+      <c r="K122" t="b">
+        <v>1</v>
+      </c>
+      <c r="L122">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="123" spans="1:12">
+      <c r="A123" t="s">
+        <v>133</v>
+      </c>
+      <c r="B123" t="s">
+        <v>152</v>
+      </c>
+      <c r="C123">
+        <v>6</v>
+      </c>
+      <c r="D123">
+        <v>11</v>
+      </c>
+      <c r="F123" t="s">
+        <v>154</v>
+      </c>
+      <c r="G123" t="s">
+        <v>156</v>
+      </c>
+      <c r="H123" t="s">
+        <v>161</v>
+      </c>
+      <c r="I123" t="s">
+        <v>168</v>
+      </c>
+      <c r="J123" t="s">
+        <v>168</v>
+      </c>
+      <c r="K123" t="b">
+        <v>1</v>
+      </c>
+      <c r="L123">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="124" spans="1:12">
+      <c r="A124" t="s">
+        <v>134</v>
+      </c>
+      <c r="B124" t="s">
+        <v>152</v>
+      </c>
+      <c r="C124">
+        <v>6</v>
+      </c>
+      <c r="D124">
+        <v>12</v>
+      </c>
+      <c r="F124" t="s">
+        <v>154</v>
+      </c>
+      <c r="G124" t="s">
+        <v>156</v>
+      </c>
+      <c r="H124" t="s">
+        <v>161</v>
+      </c>
+      <c r="I124" t="s">
+        <v>170</v>
+      </c>
+      <c r="J124" t="s">
+        <v>170</v>
+      </c>
+      <c r="K124" t="b">
+        <v>1</v>
+      </c>
+      <c r="L124">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="125" spans="1:12">
+      <c r="A125" t="s">
+        <v>135</v>
+      </c>
+      <c r="B125" t="s">
+        <v>152</v>
+      </c>
+      <c r="C125">
+        <v>8</v>
+      </c>
+      <c r="D125">
+        <v>14</v>
+      </c>
+      <c r="F125" t="s">
+        <v>155</v>
+      </c>
+      <c r="G125" t="s">
+        <v>159</v>
+      </c>
+      <c r="H125" t="s">
+        <v>164</v>
+      </c>
+      <c r="I125" t="s">
+        <v>168</v>
+      </c>
+      <c r="J125" t="s">
+        <v>168</v>
+      </c>
+      <c r="K125" t="b">
+        <v>1</v>
+      </c>
+      <c r="L125">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="126" spans="1:12">
+      <c r="A126" t="s">
+        <v>136</v>
+      </c>
+      <c r="B126" t="s">
+        <v>152</v>
+      </c>
+      <c r="C126">
+        <v>9</v>
+      </c>
+      <c r="D126">
+        <v>15</v>
+      </c>
+      <c r="F126" t="s">
+        <v>155</v>
+      </c>
+      <c r="G126" t="s">
+        <v>159</v>
+      </c>
+      <c r="H126" t="s">
+        <v>165</v>
+      </c>
+      <c r="I126" t="s">
+        <v>171</v>
+      </c>
+      <c r="J126" t="s">
+        <v>171</v>
+      </c>
+      <c r="K126" t="b">
+        <v>1</v>
+      </c>
+      <c r="L126">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="127" spans="1:12">
+      <c r="A127" t="s">
+        <v>137</v>
+      </c>
+      <c r="B127" t="s">
+        <v>152</v>
+      </c>
+      <c r="C127">
+        <v>12</v>
+      </c>
+      <c r="D127">
+        <v>18</v>
+      </c>
+      <c r="F127" t="s">
+        <v>155</v>
+      </c>
+      <c r="G127" t="s">
+        <v>157</v>
+      </c>
+      <c r="H127" t="s">
+        <v>162</v>
+      </c>
+      <c r="I127" t="s">
+        <v>170</v>
+      </c>
+      <c r="J127" t="s">
+        <v>170</v>
+      </c>
+      <c r="K127" t="b">
+        <v>1</v>
+      </c>
+      <c r="L127">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="128" spans="1:12">
+      <c r="A128" t="s">
+        <v>138</v>
+      </c>
+      <c r="B128" t="s">
+        <v>152</v>
+      </c>
+      <c r="C128">
+        <v>13</v>
+      </c>
+      <c r="D128">
+        <v>19</v>
+      </c>
+      <c r="F128" t="s">
+        <v>153</v>
+      </c>
+      <c r="G128" t="s">
+        <v>156</v>
+      </c>
+      <c r="H128" t="s">
+        <v>160</v>
+      </c>
+      <c r="I128" t="s">
+        <v>170</v>
+      </c>
+      <c r="J128" t="s">
+        <v>168</v>
+      </c>
+      <c r="K128" t="b">
+        <v>0</v>
+      </c>
+      <c r="L128">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="129" spans="1:12">
+      <c r="A129" t="s">
+        <v>139</v>
+      </c>
+      <c r="B129" t="s">
+        <v>152</v>
+      </c>
+      <c r="C129">
+        <v>4</v>
+      </c>
+      <c r="D129">
+        <v>6</v>
+      </c>
+      <c r="F129" t="s">
+        <v>154</v>
+      </c>
+      <c r="G129" t="s">
+        <v>156</v>
+      </c>
+      <c r="H129" t="s">
+        <v>161</v>
+      </c>
+      <c r="I129" t="s">
+        <v>169</v>
+      </c>
+      <c r="J129" t="s">
+        <v>169</v>
+      </c>
+      <c r="K129" t="b">
+        <v>1</v>
+      </c>
+      <c r="L129">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="130" spans="1:12">
+      <c r="A130" t="s">
+        <v>140</v>
+      </c>
+      <c r="B130" t="s">
+        <v>152</v>
+      </c>
+      <c r="C130">
+        <v>4</v>
+      </c>
+      <c r="D130">
+        <v>7</v>
+      </c>
+      <c r="F130" t="s">
+        <v>154</v>
+      </c>
+      <c r="G130" t="s">
+        <v>156</v>
+      </c>
+      <c r="H130" t="s">
+        <v>161</v>
+      </c>
+      <c r="I130" t="s">
+        <v>168</v>
+      </c>
+      <c r="J130" t="s">
+        <v>168</v>
+      </c>
+      <c r="K130" t="b">
+        <v>1</v>
+      </c>
+      <c r="L130">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="131" spans="1:12">
+      <c r="A131" t="s">
+        <v>141</v>
+      </c>
+      <c r="B131" t="s">
+        <v>152</v>
+      </c>
+      <c r="C131">
+        <v>4</v>
+      </c>
+      <c r="D131">
+        <v>8</v>
+      </c>
+      <c r="F131" t="s">
+        <v>154</v>
+      </c>
+      <c r="G131" t="s">
+        <v>156</v>
+      </c>
+      <c r="H131" t="s">
+        <v>161</v>
+      </c>
+      <c r="I131" t="s">
+        <v>168</v>
+      </c>
+      <c r="J131" t="s">
+        <v>168</v>
+      </c>
+      <c r="K131" t="b">
+        <v>1</v>
+      </c>
+      <c r="L131">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="132" spans="1:12">
+      <c r="A132" t="s">
+        <v>142</v>
+      </c>
+      <c r="B132" t="s">
+        <v>152</v>
+      </c>
+      <c r="C132">
+        <v>15</v>
+      </c>
+      <c r="D132">
+        <v>22</v>
+      </c>
+      <c r="F132" t="s">
+        <v>154</v>
+      </c>
+      <c r="G132" t="s">
+        <v>156</v>
+      </c>
+      <c r="H132" t="s">
+        <v>161</v>
+      </c>
+      <c r="I132">
+        <v>30</v>
+      </c>
+      <c r="J132">
+        <v>30</v>
+      </c>
+      <c r="K132" t="b">
+        <v>1</v>
+      </c>
+      <c r="L132">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="133" spans="1:12">
+      <c r="A133" t="s">
+        <v>143</v>
+      </c>
+      <c r="B133" t="s">
+        <v>152</v>
+      </c>
+      <c r="C133">
+        <v>15</v>
+      </c>
+      <c r="D133">
+        <v>23</v>
+      </c>
+      <c r="F133" t="s">
+        <v>154</v>
+      </c>
+      <c r="G133" t="s">
+        <v>156</v>
+      </c>
+      <c r="H133" t="s">
+        <v>161</v>
+      </c>
+      <c r="I133">
+        <v>24</v>
+      </c>
+      <c r="J133">
+        <v>24</v>
+      </c>
+      <c r="K133" t="b">
+        <v>1</v>
+      </c>
+      <c r="L133">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="134" spans="1:12">
+      <c r="A134" t="s">
+        <v>144</v>
+      </c>
+      <c r="B134" t="s">
+        <v>152</v>
+      </c>
+      <c r="C134">
+        <v>15</v>
+      </c>
+      <c r="D134">
+        <v>24</v>
+      </c>
+      <c r="F134" t="s">
+        <v>154</v>
+      </c>
+      <c r="G134" t="s">
+        <v>156</v>
+      </c>
+      <c r="H134" t="s">
+        <v>161</v>
+      </c>
+      <c r="I134">
+        <v>7</v>
+      </c>
+      <c r="J134">
+        <v>7</v>
+      </c>
+      <c r="K134" t="b">
+        <v>1</v>
+      </c>
+      <c r="L134">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="135" spans="1:12">
+      <c r="A135" t="s">
+        <v>145</v>
+      </c>
+      <c r="B135" t="s">
+        <v>152</v>
+      </c>
+      <c r="C135">
+        <v>11</v>
+      </c>
+      <c r="D135">
+        <v>17</v>
+      </c>
+      <c r="F135" t="s">
+        <v>155</v>
+      </c>
+      <c r="G135" t="s">
+        <v>158</v>
+      </c>
+      <c r="H135" t="s">
+        <v>163</v>
+      </c>
+      <c r="I135" t="s">
+        <v>171</v>
+      </c>
+      <c r="J135" t="s">
+        <v>171</v>
+      </c>
+      <c r="K135" t="b">
+        <v>1</v>
+      </c>
+      <c r="L135">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="136" spans="1:12">
+      <c r="A136" t="s">
+        <v>146</v>
+      </c>
+      <c r="B136" t="s">
+        <v>152</v>
+      </c>
+      <c r="C136">
+        <v>3</v>
+      </c>
+      <c r="D136">
+        <v>3</v>
+      </c>
+      <c r="F136" t="s">
+        <v>154</v>
+      </c>
+      <c r="G136" t="s">
+        <v>156</v>
+      </c>
+      <c r="H136" t="s">
+        <v>161</v>
+      </c>
+      <c r="I136" t="s">
+        <v>169</v>
+      </c>
+      <c r="J136" t="s">
+        <v>169</v>
+      </c>
+      <c r="K136" t="b">
+        <v>1</v>
+      </c>
+      <c r="L136">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="137" spans="1:12">
+      <c r="A137" t="s">
+        <v>147</v>
+      </c>
+      <c r="B137" t="s">
+        <v>152</v>
+      </c>
+      <c r="C137">
+        <v>3</v>
+      </c>
+      <c r="D137">
+        <v>4</v>
+      </c>
+      <c r="F137" t="s">
+        <v>154</v>
+      </c>
+      <c r="G137" t="s">
+        <v>156</v>
+      </c>
+      <c r="H137" t="s">
+        <v>161</v>
+      </c>
+      <c r="I137" t="s">
+        <v>170</v>
+      </c>
+      <c r="J137" t="s">
+        <v>170</v>
+      </c>
+      <c r="K137" t="b">
+        <v>1</v>
+      </c>
+      <c r="L137">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="138" spans="1:12">
+      <c r="A138" t="s">
+        <v>148</v>
+      </c>
+      <c r="B138" t="s">
+        <v>152</v>
+      </c>
+      <c r="C138">
+        <v>3</v>
+      </c>
+      <c r="D138">
+        <v>5</v>
+      </c>
+      <c r="F138" t="s">
+        <v>154</v>
+      </c>
+      <c r="G138" t="s">
+        <v>156</v>
+      </c>
+      <c r="H138" t="s">
+        <v>161</v>
+      </c>
+      <c r="I138" t="s">
+        <v>171</v>
+      </c>
+      <c r="J138" t="s">
+        <v>171</v>
+      </c>
+      <c r="K138" t="b">
+        <v>1</v>
+      </c>
+      <c r="L138">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="139" spans="1:12">
+      <c r="A139" t="s">
+        <v>149</v>
+      </c>
+      <c r="B139" t="s">
+        <v>152</v>
+      </c>
+      <c r="C139">
+        <v>12</v>
+      </c>
+      <c r="D139">
+        <v>18</v>
+      </c>
+      <c r="F139" t="s">
+        <v>155</v>
+      </c>
+      <c r="G139" t="s">
+        <v>157</v>
+      </c>
+      <c r="H139" t="s">
+        <v>162</v>
+      </c>
+      <c r="I139" t="s">
+        <v>172</v>
+      </c>
+      <c r="J139" t="s">
+        <v>170</v>
+      </c>
+      <c r="K139" t="b">
+        <v>0</v>
+      </c>
+      <c r="L139">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
